--- a/user-stories/example-files/on-the-day-2.xlsx
+++ b/user-stories/example-files/on-the-day-2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fcc7848ed757d0c/Pitsea/C2C/2026/April 2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Personal\pitsea-rc-results-processing\user-stories\example-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{9BE5BAB3-8307-4E80-9936-0CC8229E35A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5EE601F5-A080-433C-8BCC-734AA57EEDA6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{797D3F31-63D2-4375-81A0-7093DBFDCDE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1536" windowWidth="11712" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="On The Day" sheetId="7" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="138">
   <si>
     <t>Race No</t>
   </si>
@@ -885,19 +885,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I703"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I700"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" style="2" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="31.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.44140625" customWidth="1"/>
-    <col min="7" max="7" width="3.77734375" customWidth="1"/>
+    <col min="3" max="3" width="31.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" customWidth="1"/>
+    <col min="7" max="7" width="3.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -917,7 +917,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -936,7 +936,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>2</v>
       </c>
@@ -953,7 +953,7 @@
       <c r="F3" s="7"/>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>3</v>
       </c>
@@ -972,7 +972,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>4</v>
       </c>
@@ -992,7 +992,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>5</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>6</v>
       </c>
@@ -1034,7 +1034,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>7</v>
       </c>
@@ -1050,7 +1050,7 @@
       <c r="E8" s="6"/>
       <c r="F8" s="7"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>8</v>
       </c>
@@ -1066,7 +1066,7 @@
       <c r="E9" s="6"/>
       <c r="F9" s="7"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>9</v>
       </c>
@@ -1082,7 +1082,7 @@
       <c r="E10" s="6"/>
       <c r="F10" s="7"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>10</v>
       </c>
@@ -1098,7 +1098,7 @@
       <c r="E11" s="6"/>
       <c r="F11" s="7"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>11</v>
       </c>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="F12" s="7"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>12</v>
       </c>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="F13" s="7"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>13</v>
       </c>
@@ -1150,7 +1150,7 @@
       <c r="E14" s="6"/>
       <c r="F14" s="7"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>14</v>
       </c>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="F15" s="7"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>15</v>
       </c>
@@ -1184,7 +1184,7 @@
       <c r="E16" s="6"/>
       <c r="F16" s="7"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>16</v>
       </c>
@@ -1200,7 +1200,7 @@
       <c r="E17" s="6"/>
       <c r="F17" s="7"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>17</v>
       </c>
@@ -1216,7 +1216,7 @@
       <c r="E18" s="6"/>
       <c r="F18" s="7"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>18</v>
       </c>
@@ -1232,7 +1232,7 @@
       <c r="E19" s="6"/>
       <c r="F19" s="7"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>19</v>
       </c>
@@ -1248,7 +1248,7 @@
       <c r="E20" s="6"/>
       <c r="F20" s="7"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>20</v>
       </c>
@@ -1264,7 +1264,7 @@
       <c r="E21" s="6"/>
       <c r="F21" s="7"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>21</v>
       </c>
@@ -1280,7 +1280,7 @@
       <c r="E22" s="6"/>
       <c r="F22" s="7"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>22</v>
       </c>
@@ -1296,7 +1296,7 @@
       <c r="E23" s="6"/>
       <c r="F23" s="7"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>23</v>
       </c>
@@ -1312,7 +1312,7 @@
       <c r="E24" s="6"/>
       <c r="F24" s="7"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>24</v>
       </c>
@@ -1328,7 +1328,7 @@
       <c r="E25" s="6"/>
       <c r="F25" s="7"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>25</v>
       </c>
@@ -1344,7 +1344,7 @@
       <c r="E26" s="6"/>
       <c r="F26" s="7"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>26</v>
       </c>
@@ -1360,7 +1360,7 @@
       <c r="E27" s="6"/>
       <c r="F27" s="7"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>27</v>
       </c>
@@ -1376,7 +1376,7 @@
       <c r="E28" s="6"/>
       <c r="F28" s="7"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>28</v>
       </c>
@@ -1392,7 +1392,7 @@
       <c r="E29" s="6"/>
       <c r="F29" s="7"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>29</v>
       </c>
@@ -1408,7 +1408,7 @@
       <c r="E30" s="6"/>
       <c r="F30" s="7"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>30</v>
       </c>
@@ -1422,7 +1422,7 @@
       <c r="E31" s="6"/>
       <c r="F31" s="7"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>31</v>
       </c>
@@ -1438,7 +1438,7 @@
       <c r="E32" s="6"/>
       <c r="F32" s="7"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>32</v>
       </c>
@@ -1454,7 +1454,7 @@
       <c r="E33" s="6"/>
       <c r="F33" s="7"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>33</v>
       </c>
@@ -1470,7 +1470,7 @@
       <c r="E34" s="6"/>
       <c r="F34" s="7"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>34</v>
       </c>
@@ -1486,7 +1486,7 @@
       <c r="E35" s="6"/>
       <c r="F35" s="7"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>35</v>
       </c>
@@ -1502,7 +1502,7 @@
       <c r="E36" s="6"/>
       <c r="F36" s="7"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>36</v>
       </c>
@@ -1516,7 +1516,7 @@
       <c r="E37" s="6"/>
       <c r="F37" s="7"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>37</v>
       </c>
@@ -1532,7 +1532,7 @@
       <c r="E38" s="6"/>
       <c r="F38" s="7"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>38</v>
       </c>
@@ -1548,7 +1548,7 @@
       <c r="E39" s="6"/>
       <c r="F39" s="7"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>39</v>
       </c>
@@ -1562,7 +1562,7 @@
       <c r="E40" s="6"/>
       <c r="F40" s="7"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>40</v>
       </c>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="F41" s="7"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>41</v>
       </c>
@@ -1594,7 +1594,7 @@
       <c r="E42" s="6"/>
       <c r="F42" s="7"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>42</v>
       </c>
@@ -1608,7 +1608,7 @@
       <c r="E43" s="6"/>
       <c r="F43" s="7"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>43</v>
       </c>
@@ -1624,7 +1624,7 @@
       <c r="E44" s="6"/>
       <c r="F44" s="7"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>44</v>
       </c>
@@ -1640,7 +1640,7 @@
       <c r="E45" s="6"/>
       <c r="F45" s="7"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>45</v>
       </c>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="F46" s="7"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>46</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>47</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>48</v>
       </c>
@@ -1710,7 +1710,7 @@
       <c r="E49" s="6"/>
       <c r="F49" s="7"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>49</v>
       </c>
@@ -1726,7 +1726,7 @@
       <c r="E50" s="6"/>
       <c r="F50" s="7"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>50</v>
       </c>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="F51" s="7"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>51</v>
       </c>
@@ -1760,7 +1760,7 @@
       <c r="E52" s="6"/>
       <c r="F52" s="7"/>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>52</v>
       </c>
@@ -1776,7 +1776,7 @@
       <c r="E53" s="6"/>
       <c r="F53" s="7"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>53</v>
       </c>
@@ -1792,7 +1792,7 @@
       <c r="E54" s="6"/>
       <c r="F54" s="7"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>54</v>
       </c>
@@ -1806,7 +1806,7 @@
       <c r="E55" s="6"/>
       <c r="F55" s="7"/>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>55</v>
       </c>
@@ -1822,7 +1822,7 @@
       <c r="E56" s="6"/>
       <c r="F56" s="7"/>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>56</v>
       </c>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="F57" s="7"/>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>57</v>
       </c>
@@ -1852,7 +1852,7 @@
       <c r="E58" s="6"/>
       <c r="F58" s="7"/>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>58</v>
       </c>
@@ -1866,7 +1866,7 @@
       <c r="E59" s="6"/>
       <c r="F59" s="7"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>59</v>
       </c>
@@ -1882,7 +1882,7 @@
       <c r="E60" s="6"/>
       <c r="F60" s="7"/>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>60</v>
       </c>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="F61" s="7"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>61</v>
       </c>
@@ -1912,7 +1912,7 @@
       <c r="E62" s="6"/>
       <c r="F62" s="7"/>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>62</v>
       </c>
@@ -1928,7 +1928,7 @@
       <c r="E63" s="6"/>
       <c r="F63" s="7"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>63</v>
       </c>
@@ -1944,7 +1944,7 @@
       <c r="E64" s="6"/>
       <c r="F64" s="7"/>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>64</v>
       </c>
@@ -1960,7 +1960,7 @@
       <c r="E65" s="6"/>
       <c r="F65" s="7"/>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>65</v>
       </c>
@@ -1976,7 +1976,7 @@
       <c r="E66" s="6"/>
       <c r="F66" s="7"/>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>66</v>
       </c>
@@ -1990,7 +1990,7 @@
       <c r="E67" s="6"/>
       <c r="F67" s="7"/>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>67</v>
       </c>
@@ -2004,7 +2004,7 @@
       <c r="E68" s="6"/>
       <c r="F68" s="7"/>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>68</v>
       </c>
@@ -2020,14 +2020,14 @@
       <c r="E69" s="6"/>
       <c r="F69" s="7"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="6"/>
       <c r="B70" s="7"/>
       <c r="C70" s="7"/>
       <c r="E70" s="6"/>
       <c r="F70" s="7"/>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="6"/>
       <c r="B71" s="7"/>
       <c r="C71" s="7"/>
@@ -2035,7 +2035,7 @@
       <c r="E71" s="6"/>
       <c r="F71" s="7"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="6"/>
       <c r="B72" s="7"/>
       <c r="C72" s="7"/>
@@ -2043,7 +2043,7 @@
       <c r="E72" s="6"/>
       <c r="F72" s="7"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="6"/>
       <c r="B73" s="7"/>
       <c r="C73" s="7"/>
@@ -2051,7 +2051,7 @@
       <c r="E73" s="6"/>
       <c r="F73" s="7"/>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="6"/>
       <c r="B74" s="7"/>
       <c r="C74" s="7"/>
@@ -2059,7 +2059,7 @@
       <c r="E74" s="6"/>
       <c r="F74" s="7"/>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="6"/>
       <c r="B75" s="7"/>
       <c r="C75" s="7"/>
@@ -2067,7 +2067,7 @@
       <c r="E75" s="6"/>
       <c r="F75" s="7"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="6"/>
       <c r="B76" s="7"/>
       <c r="C76" s="7"/>
@@ -2075,7 +2075,7 @@
       <c r="E76" s="6"/>
       <c r="F76" s="7"/>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="6"/>
       <c r="B77" s="7"/>
       <c r="C77" s="7"/>
@@ -2083,7 +2083,7 @@
       <c r="E77" s="6"/>
       <c r="F77" s="7"/>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="6"/>
       <c r="B78" s="7"/>
       <c r="C78" s="7"/>
@@ -2091,7 +2091,7 @@
       <c r="E78" s="6"/>
       <c r="F78" s="7"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="6"/>
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
@@ -2099,7 +2099,7 @@
       <c r="E79" s="6"/>
       <c r="F79" s="7"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="6"/>
       <c r="B80" s="7"/>
       <c r="C80" s="7"/>
@@ -2107,7 +2107,7 @@
       <c r="E80" s="6"/>
       <c r="F80" s="7"/>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="6"/>
       <c r="B81" s="7"/>
       <c r="C81" s="7"/>
@@ -2115,7 +2115,7 @@
       <c r="E81" s="6"/>
       <c r="F81" s="7"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="6"/>
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
@@ -2123,7 +2123,7 @@
       <c r="E82" s="6"/>
       <c r="F82" s="7"/>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="6"/>
       <c r="B83" s="7"/>
       <c r="C83" s="7"/>
@@ -2131,7 +2131,7 @@
       <c r="E83" s="6"/>
       <c r="F83" s="7"/>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="6"/>
       <c r="B84" s="7"/>
       <c r="C84" s="7"/>
@@ -2139,7 +2139,7 @@
       <c r="E84" s="6"/>
       <c r="F84" s="7"/>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="6"/>
       <c r="B85" s="7"/>
       <c r="C85" s="7"/>
@@ -2147,7 +2147,7 @@
       <c r="E85" s="6"/>
       <c r="F85" s="7"/>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="6"/>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
@@ -2155,7 +2155,7 @@
       <c r="E86" s="6"/>
       <c r="F86" s="7"/>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="6"/>
       <c r="B87" s="7"/>
       <c r="C87" s="7"/>
@@ -2163,7 +2163,7 @@
       <c r="E87" s="6"/>
       <c r="F87" s="7"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="6"/>
       <c r="B88" s="7"/>
       <c r="C88" s="7"/>
@@ -2171,7 +2171,7 @@
       <c r="E88" s="6"/>
       <c r="F88" s="7"/>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="6"/>
       <c r="B89" s="7"/>
       <c r="C89" s="7"/>
@@ -2179,7 +2179,7 @@
       <c r="E89" s="6"/>
       <c r="F89" s="7"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="6"/>
       <c r="B90" s="7"/>
       <c r="C90" s="7"/>
@@ -2187,7 +2187,7 @@
       <c r="E90" s="6"/>
       <c r="F90" s="7"/>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="6"/>
       <c r="B91" s="7"/>
       <c r="C91" s="7"/>
@@ -2195,7 +2195,7 @@
       <c r="E91" s="6"/>
       <c r="F91" s="7"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="6"/>
       <c r="B92" s="7"/>
       <c r="C92" s="7"/>
@@ -2203,7 +2203,7 @@
       <c r="E92" s="6"/>
       <c r="F92" s="7"/>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="6"/>
       <c r="B93" s="7"/>
       <c r="C93" s="7"/>
@@ -2211,7 +2211,7 @@
       <c r="E93" s="6"/>
       <c r="F93" s="7"/>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="6"/>
       <c r="B94" s="7"/>
       <c r="C94" s="7"/>
@@ -2219,7 +2219,7 @@
       <c r="E94" s="6"/>
       <c r="F94" s="7"/>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="6"/>
       <c r="B95" s="7"/>
       <c r="C95" s="7"/>
@@ -2227,7 +2227,7 @@
       <c r="E95" s="6"/>
       <c r="F95" s="7"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="6"/>
       <c r="B96" s="7"/>
       <c r="C96" s="7"/>
@@ -2235,7 +2235,7 @@
       <c r="E96" s="6"/>
       <c r="F96" s="7"/>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="6"/>
       <c r="B97" s="7"/>
       <c r="C97" s="7"/>
@@ -2243,7 +2243,7 @@
       <c r="E97" s="6"/>
       <c r="F97" s="7"/>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="6"/>
       <c r="B98" s="7"/>
       <c r="C98" s="7"/>
@@ -2251,7 +2251,7 @@
       <c r="E98" s="6"/>
       <c r="F98" s="7"/>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="6"/>
       <c r="B99" s="7"/>
       <c r="C99" s="7"/>
@@ -2259,7 +2259,7 @@
       <c r="E99" s="6"/>
       <c r="F99" s="7"/>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="6"/>
       <c r="B100" s="7"/>
       <c r="C100" s="7"/>
@@ -2267,7 +2267,7 @@
       <c r="E100" s="6"/>
       <c r="F100" s="7"/>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="6"/>
       <c r="B101" s="7"/>
       <c r="C101" s="7"/>
@@ -2275,7 +2275,7 @@
       <c r="E101" s="6"/>
       <c r="F101" s="7"/>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="6"/>
       <c r="B102" s="7"/>
       <c r="C102" s="7"/>
@@ -2283,7 +2283,7 @@
       <c r="E102" s="6"/>
       <c r="F102" s="7"/>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="6"/>
       <c r="B103" s="7"/>
       <c r="C103" s="7"/>
@@ -2291,7 +2291,7 @@
       <c r="E103" s="6"/>
       <c r="F103" s="7"/>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="6"/>
       <c r="B104" s="7"/>
       <c r="C104" s="7"/>
@@ -2299,7 +2299,7 @@
       <c r="E104" s="6"/>
       <c r="F104" s="7"/>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="6"/>
       <c r="B105" s="7"/>
       <c r="C105" s="7"/>
@@ -2307,7 +2307,7 @@
       <c r="E105" s="6"/>
       <c r="F105" s="7"/>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="6"/>
       <c r="B106" s="7"/>
       <c r="C106" s="7"/>
@@ -2315,7 +2315,7 @@
       <c r="E106" s="6"/>
       <c r="F106" s="7"/>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="6"/>
       <c r="B107" s="7"/>
       <c r="C107" s="7"/>
@@ -2323,7 +2323,7 @@
       <c r="E107" s="6"/>
       <c r="F107" s="7"/>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="6"/>
       <c r="B108" s="7"/>
       <c r="C108" s="7"/>
@@ -2331,7 +2331,7 @@
       <c r="E108" s="6"/>
       <c r="F108" s="7"/>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="6"/>
       <c r="B109" s="7"/>
       <c r="C109" s="7"/>
@@ -2339,7 +2339,7 @@
       <c r="E109" s="6"/>
       <c r="F109" s="7"/>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="6"/>
       <c r="B110" s="7"/>
       <c r="C110" s="7"/>
@@ -2347,7 +2347,7 @@
       <c r="E110" s="6"/>
       <c r="F110" s="7"/>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="6"/>
       <c r="B111" s="7"/>
       <c r="C111" s="7"/>
@@ -2355,7 +2355,7 @@
       <c r="E111" s="6"/>
       <c r="F111" s="7"/>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="6"/>
       <c r="B112" s="7"/>
       <c r="C112" s="7"/>
@@ -2363,7 +2363,7 @@
       <c r="E112" s="6"/>
       <c r="F112" s="7"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="6"/>
       <c r="B113" s="7"/>
       <c r="C113" s="7"/>
@@ -2371,7 +2371,7 @@
       <c r="E113" s="6"/>
       <c r="F113" s="7"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="6"/>
       <c r="B114" s="7"/>
       <c r="C114" s="7"/>
@@ -2379,7 +2379,7 @@
       <c r="E114" s="6"/>
       <c r="F114" s="7"/>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="6"/>
       <c r="B115" s="7"/>
       <c r="C115" s="7"/>
@@ -2387,7 +2387,7 @@
       <c r="E115" s="6"/>
       <c r="F115" s="7"/>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="6"/>
       <c r="B116" s="7"/>
       <c r="C116" s="7"/>
@@ -2395,7 +2395,7 @@
       <c r="E116" s="6"/>
       <c r="F116" s="7"/>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="6"/>
       <c r="B117" s="7"/>
       <c r="C117" s="7"/>
@@ -2403,7 +2403,7 @@
       <c r="E117" s="6"/>
       <c r="F117" s="7"/>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="6"/>
       <c r="B118" s="7"/>
       <c r="C118" s="7"/>
@@ -2411,7 +2411,7 @@
       <c r="E118" s="6"/>
       <c r="F118" s="7"/>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="6"/>
       <c r="B119" s="7"/>
       <c r="C119" s="7"/>
@@ -2419,7 +2419,7 @@
       <c r="E119" s="6"/>
       <c r="F119" s="7"/>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="6"/>
       <c r="B120" s="7"/>
       <c r="C120" s="7"/>
@@ -2427,7 +2427,7 @@
       <c r="E120" s="6"/>
       <c r="F120" s="7"/>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="6"/>
       <c r="B121" s="7"/>
       <c r="C121" s="7"/>
@@ -2435,7 +2435,7 @@
       <c r="E121" s="6"/>
       <c r="F121" s="7"/>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="6"/>
       <c r="B122" s="7"/>
       <c r="C122" s="7"/>
@@ -2443,7 +2443,7 @@
       <c r="E122" s="6"/>
       <c r="F122" s="7"/>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="6"/>
       <c r="B123" s="7"/>
       <c r="C123" s="7"/>
@@ -2451,7 +2451,7 @@
       <c r="E123" s="6"/>
       <c r="F123" s="7"/>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="6"/>
       <c r="B124" s="7"/>
       <c r="C124" s="7"/>
@@ -2459,7 +2459,7 @@
       <c r="E124" s="6"/>
       <c r="F124" s="7"/>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="6"/>
       <c r="B125" s="7"/>
       <c r="C125" s="7"/>
@@ -2467,7 +2467,7 @@
       <c r="E125" s="6"/>
       <c r="F125" s="7"/>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="6"/>
       <c r="B126" s="7"/>
       <c r="C126" s="7"/>
@@ -2475,7 +2475,7 @@
       <c r="E126" s="6"/>
       <c r="F126" s="7"/>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="6"/>
       <c r="B127" s="7"/>
       <c r="C127" s="7"/>
@@ -2483,7 +2483,7 @@
       <c r="E127" s="6"/>
       <c r="F127" s="7"/>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="6"/>
       <c r="B128" s="7"/>
       <c r="C128" s="7"/>
@@ -2491,7 +2491,7 @@
       <c r="E128" s="6"/>
       <c r="F128" s="7"/>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="6"/>
       <c r="B129" s="7"/>
       <c r="C129" s="7"/>
@@ -2499,7 +2499,7 @@
       <c r="E129" s="6"/>
       <c r="F129" s="7"/>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="6"/>
       <c r="B130" s="7"/>
       <c r="C130" s="7"/>
@@ -2507,7 +2507,7 @@
       <c r="E130" s="6"/>
       <c r="F130" s="7"/>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="6"/>
       <c r="B131" s="7"/>
       <c r="C131" s="7"/>
@@ -2515,7 +2515,7 @@
       <c r="E131" s="6"/>
       <c r="F131" s="7"/>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="6"/>
       <c r="B132" s="7"/>
       <c r="C132" s="7"/>
@@ -2523,7 +2523,7 @@
       <c r="E132" s="6"/>
       <c r="F132" s="7"/>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="6"/>
       <c r="B133" s="7"/>
       <c r="C133" s="7"/>
@@ -2531,7 +2531,7 @@
       <c r="E133" s="6"/>
       <c r="F133" s="7"/>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="6"/>
       <c r="B134" s="7"/>
       <c r="C134" s="7"/>
@@ -2539,7 +2539,7 @@
       <c r="E134" s="6"/>
       <c r="F134" s="7"/>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="6"/>
       <c r="B135" s="7"/>
       <c r="C135" s="7"/>
@@ -2547,7 +2547,7 @@
       <c r="E135" s="6"/>
       <c r="F135" s="7"/>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="6"/>
       <c r="B136" s="7"/>
       <c r="C136" s="7"/>
@@ -2555,7 +2555,7 @@
       <c r="E136" s="6"/>
       <c r="F136" s="7"/>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="6"/>
       <c r="B137" s="7"/>
       <c r="C137" s="7"/>
@@ -2563,7 +2563,7 @@
       <c r="E137" s="6"/>
       <c r="F137" s="7"/>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="6"/>
       <c r="B138" s="7"/>
       <c r="C138" s="7"/>
@@ -2571,7 +2571,7 @@
       <c r="E138" s="6"/>
       <c r="F138" s="7"/>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="6"/>
       <c r="B139" s="7"/>
       <c r="C139" s="7"/>
@@ -2579,7 +2579,7 @@
       <c r="E139" s="6"/>
       <c r="F139" s="7"/>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="6"/>
       <c r="B140" s="7"/>
       <c r="C140" s="7"/>
@@ -2587,7 +2587,7 @@
       <c r="E140" s="6"/>
       <c r="F140" s="7"/>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="6"/>
       <c r="B141" s="7"/>
       <c r="C141" s="7"/>
@@ -2595,7 +2595,7 @@
       <c r="E141" s="6"/>
       <c r="F141" s="7"/>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="6"/>
       <c r="B142" s="7"/>
       <c r="C142" s="7"/>
@@ -2603,7 +2603,7 @@
       <c r="E142" s="6"/>
       <c r="F142" s="7"/>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="6"/>
       <c r="B143" s="7"/>
       <c r="C143" s="7"/>
@@ -2611,7 +2611,7 @@
       <c r="E143" s="6"/>
       <c r="F143" s="7"/>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="6"/>
       <c r="B144" s="7"/>
       <c r="C144" s="7"/>
@@ -2619,7 +2619,7 @@
       <c r="E144" s="6"/>
       <c r="F144" s="7"/>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="6"/>
       <c r="B145" s="7"/>
       <c r="C145" s="7"/>
@@ -2627,7 +2627,7 @@
       <c r="E145" s="6"/>
       <c r="F145" s="7"/>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="6"/>
       <c r="B146" s="7"/>
       <c r="C146" s="7"/>
@@ -2635,7 +2635,7 @@
       <c r="E146" s="6"/>
       <c r="F146" s="7"/>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="6"/>
       <c r="B147" s="7"/>
       <c r="C147" s="7"/>
@@ -2643,7 +2643,7 @@
       <c r="E147" s="6"/>
       <c r="F147" s="7"/>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="6"/>
       <c r="B148" s="7"/>
       <c r="C148" s="7"/>
@@ -2651,7 +2651,7 @@
       <c r="E148" s="6"/>
       <c r="F148" s="7"/>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="6"/>
       <c r="B149" s="7"/>
       <c r="C149" s="7"/>
@@ -2659,7 +2659,7 @@
       <c r="E149" s="6"/>
       <c r="F149" s="7"/>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="6"/>
       <c r="B150" s="7"/>
       <c r="C150" s="7"/>
@@ -2667,7 +2667,7 @@
       <c r="E150" s="6"/>
       <c r="F150" s="7"/>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="6"/>
       <c r="B151" s="7"/>
       <c r="C151" s="7"/>
@@ -2675,7 +2675,7 @@
       <c r="E151" s="6"/>
       <c r="F151" s="7"/>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="6"/>
       <c r="B152" s="7"/>
       <c r="C152" s="7"/>
@@ -2683,7 +2683,7 @@
       <c r="E152" s="6"/>
       <c r="F152" s="7"/>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="6"/>
       <c r="B153" s="7"/>
       <c r="C153" s="7"/>
@@ -2691,7 +2691,7 @@
       <c r="E153" s="6"/>
       <c r="F153" s="7"/>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="6"/>
       <c r="B154" s="7"/>
       <c r="C154" s="7"/>
@@ -2699,7 +2699,7 @@
       <c r="E154" s="6"/>
       <c r="F154" s="7"/>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="6"/>
       <c r="B155" s="7"/>
       <c r="C155" s="7"/>
@@ -2707,7 +2707,7 @@
       <c r="E155" s="6"/>
       <c r="F155" s="7"/>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="6"/>
       <c r="B156" s="7"/>
       <c r="C156" s="7"/>
@@ -2715,7 +2715,7 @@
       <c r="E156" s="6"/>
       <c r="F156" s="7"/>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="6"/>
       <c r="B157" s="7"/>
       <c r="C157" s="7"/>
@@ -2723,7 +2723,7 @@
       <c r="E157" s="6"/>
       <c r="F157" s="7"/>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="6"/>
       <c r="B158" s="7"/>
       <c r="C158" s="7"/>
@@ -2731,7 +2731,7 @@
       <c r="E158" s="6"/>
       <c r="F158" s="7"/>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="6"/>
       <c r="B159" s="7"/>
       <c r="C159" s="7"/>
@@ -2739,7 +2739,7 @@
       <c r="E159" s="6"/>
       <c r="F159" s="7"/>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="6"/>
       <c r="B160" s="7"/>
       <c r="C160" s="7"/>
@@ -2747,7 +2747,7 @@
       <c r="E160" s="6"/>
       <c r="F160" s="7"/>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="6"/>
       <c r="B161" s="7"/>
       <c r="C161" s="7"/>
@@ -2755,7 +2755,7 @@
       <c r="E161" s="6"/>
       <c r="F161" s="7"/>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="6"/>
       <c r="B162" s="7"/>
       <c r="C162" s="7"/>
@@ -2763,7 +2763,7 @@
       <c r="E162" s="6"/>
       <c r="F162" s="7"/>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="6"/>
       <c r="B163" s="7"/>
       <c r="C163" s="7"/>
@@ -2771,7 +2771,7 @@
       <c r="E163" s="6"/>
       <c r="F163" s="7"/>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="6"/>
       <c r="B164" s="7"/>
       <c r="C164" s="7"/>
@@ -2779,7 +2779,7 @@
       <c r="E164" s="6"/>
       <c r="F164" s="7"/>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="6"/>
       <c r="B165" s="7"/>
       <c r="C165" s="7"/>
@@ -2787,7 +2787,7 @@
       <c r="E165" s="6"/>
       <c r="F165" s="7"/>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="6"/>
       <c r="B166" s="7"/>
       <c r="C166" s="7"/>
@@ -2795,7 +2795,7 @@
       <c r="E166" s="6"/>
       <c r="F166" s="7"/>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="6"/>
       <c r="B167" s="7"/>
       <c r="C167" s="7"/>
@@ -2803,7 +2803,7 @@
       <c r="E167" s="6"/>
       <c r="F167" s="7"/>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="6"/>
       <c r="B168" s="7"/>
       <c r="C168" s="7"/>
@@ -2811,7 +2811,7 @@
       <c r="E168" s="6"/>
       <c r="F168" s="7"/>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="6"/>
       <c r="B169" s="7"/>
       <c r="C169" s="7"/>
@@ -2819,7 +2819,7 @@
       <c r="E169" s="6"/>
       <c r="F169" s="7"/>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="6"/>
       <c r="B170" s="7"/>
       <c r="C170" s="7"/>
@@ -2827,7 +2827,7 @@
       <c r="E170" s="6"/>
       <c r="F170" s="7"/>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="6"/>
       <c r="B171" s="7"/>
       <c r="C171" s="7"/>
@@ -2835,7 +2835,7 @@
       <c r="E171" s="6"/>
       <c r="F171" s="7"/>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="6"/>
       <c r="B172" s="7"/>
       <c r="C172" s="7"/>
@@ -2843,7 +2843,7 @@
       <c r="E172" s="6"/>
       <c r="F172" s="7"/>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="6"/>
       <c r="B173" s="7"/>
       <c r="C173" s="7"/>
@@ -2851,7 +2851,7 @@
       <c r="E173" s="6"/>
       <c r="F173" s="7"/>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="6"/>
       <c r="B174" s="7"/>
       <c r="C174" s="7"/>
@@ -2859,7 +2859,7 @@
       <c r="E174" s="6"/>
       <c r="F174" s="7"/>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="6"/>
       <c r="B175" s="7"/>
       <c r="C175" s="7"/>
@@ -2867,7 +2867,7 @@
       <c r="E175" s="6"/>
       <c r="F175" s="7"/>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="6"/>
       <c r="B176" s="7"/>
       <c r="C176" s="7"/>
@@ -2875,7 +2875,7 @@
       <c r="E176" s="6"/>
       <c r="F176" s="7"/>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="6"/>
       <c r="B177" s="7"/>
       <c r="C177" s="7"/>
@@ -2883,7 +2883,7 @@
       <c r="E177" s="6"/>
       <c r="F177" s="7"/>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="6"/>
       <c r="B178" s="7"/>
       <c r="C178" s="7"/>
@@ -2891,7 +2891,7 @@
       <c r="E178" s="6"/>
       <c r="F178" s="7"/>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="6"/>
       <c r="B179" s="7"/>
       <c r="C179" s="7"/>
@@ -2899,7 +2899,7 @@
       <c r="E179" s="6"/>
       <c r="F179" s="7"/>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="6"/>
       <c r="B180" s="7"/>
       <c r="C180" s="7"/>
@@ -2907,7 +2907,7 @@
       <c r="E180" s="6"/>
       <c r="F180" s="7"/>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="6"/>
       <c r="B181" s="7"/>
       <c r="C181" s="7"/>
@@ -2915,7 +2915,7 @@
       <c r="E181" s="6"/>
       <c r="F181" s="7"/>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="6"/>
       <c r="B182" s="7"/>
       <c r="C182" s="7"/>
@@ -2923,7 +2923,7 @@
       <c r="E182" s="6"/>
       <c r="F182" s="7"/>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="6"/>
       <c r="B183" s="7"/>
       <c r="C183" s="7"/>
@@ -2931,7 +2931,7 @@
       <c r="E183" s="6"/>
       <c r="F183" s="7"/>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="6"/>
       <c r="B184" s="7"/>
       <c r="C184" s="7"/>
@@ -2939,7 +2939,7 @@
       <c r="E184" s="6"/>
       <c r="F184" s="7"/>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="6"/>
       <c r="B185" s="7"/>
       <c r="C185" s="7"/>
@@ -2947,7 +2947,7 @@
       <c r="E185" s="6"/>
       <c r="F185" s="7"/>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="6"/>
       <c r="B186" s="7"/>
       <c r="C186" s="7"/>
@@ -2955,7 +2955,7 @@
       <c r="E186" s="6"/>
       <c r="F186" s="7"/>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="6"/>
       <c r="B187" s="7"/>
       <c r="C187" s="7"/>
@@ -2963,7 +2963,7 @@
       <c r="E187" s="6"/>
       <c r="F187" s="7"/>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="6"/>
       <c r="B188" s="7"/>
       <c r="C188" s="7"/>
@@ -2971,7 +2971,7 @@
       <c r="E188" s="6"/>
       <c r="F188" s="7"/>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="6"/>
       <c r="B189" s="7"/>
       <c r="C189" s="7"/>
@@ -2979,7 +2979,7 @@
       <c r="E189" s="6"/>
       <c r="F189" s="7"/>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="6"/>
       <c r="B190" s="7"/>
       <c r="C190" s="7"/>
@@ -2987,7 +2987,7 @@
       <c r="E190" s="6"/>
       <c r="F190" s="7"/>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="6"/>
       <c r="B191" s="7"/>
       <c r="C191" s="7"/>
@@ -2995,7 +2995,7 @@
       <c r="E191" s="6"/>
       <c r="F191" s="7"/>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="6"/>
       <c r="B192" s="7"/>
       <c r="C192" s="7"/>
@@ -3003,7 +3003,7 @@
       <c r="E192" s="6"/>
       <c r="F192" s="7"/>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="6"/>
       <c r="B193" s="7"/>
       <c r="C193" s="7"/>
@@ -3011,7 +3011,7 @@
       <c r="E193" s="6"/>
       <c r="F193" s="7"/>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="6"/>
       <c r="B194" s="7"/>
       <c r="C194" s="7"/>
@@ -3019,7 +3019,7 @@
       <c r="E194" s="6"/>
       <c r="F194" s="7"/>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="6"/>
       <c r="B195" s="7"/>
       <c r="C195" s="7"/>
@@ -3027,7 +3027,7 @@
       <c r="E195" s="6"/>
       <c r="F195" s="7"/>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="6"/>
       <c r="B196" s="7"/>
       <c r="C196" s="7"/>
@@ -3035,7 +3035,7 @@
       <c r="E196" s="6"/>
       <c r="F196" s="7"/>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="6"/>
       <c r="B197" s="7"/>
       <c r="C197" s="7"/>
@@ -3043,7 +3043,7 @@
       <c r="E197" s="6"/>
       <c r="F197" s="7"/>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="6"/>
       <c r="B198" s="7"/>
       <c r="C198" s="7"/>
@@ -3051,7 +3051,7 @@
       <c r="E198" s="6"/>
       <c r="F198" s="7"/>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="6"/>
       <c r="B199" s="7"/>
       <c r="C199" s="7"/>
@@ -3059,7 +3059,7 @@
       <c r="E199" s="6"/>
       <c r="F199" s="7"/>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="6"/>
       <c r="B200" s="7"/>
       <c r="C200" s="7"/>
@@ -3067,7 +3067,7 @@
       <c r="E200" s="6"/>
       <c r="F200" s="7"/>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="6"/>
       <c r="B201" s="7"/>
       <c r="C201" s="7"/>
@@ -3075,7 +3075,7 @@
       <c r="E201" s="6"/>
       <c r="F201" s="7"/>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="6"/>
       <c r="B202" s="7"/>
       <c r="C202" s="7"/>
@@ -3083,7 +3083,7 @@
       <c r="E202" s="6"/>
       <c r="F202" s="7"/>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="6"/>
       <c r="B203" s="7"/>
       <c r="C203" s="7"/>
@@ -3091,7 +3091,7 @@
       <c r="E203" s="6"/>
       <c r="F203" s="7"/>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="6"/>
       <c r="B204" s="7"/>
       <c r="C204" s="7"/>
@@ -3099,7 +3099,7 @@
       <c r="E204" s="6"/>
       <c r="F204" s="7"/>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="6"/>
       <c r="B205" s="7"/>
       <c r="C205" s="7"/>
@@ -3107,7 +3107,7 @@
       <c r="E205" s="6"/>
       <c r="F205" s="7"/>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="6"/>
       <c r="B206" s="7"/>
       <c r="C206" s="7"/>
@@ -3115,7 +3115,7 @@
       <c r="E206" s="6"/>
       <c r="F206" s="7"/>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="6"/>
       <c r="B207" s="7"/>
       <c r="C207" s="7"/>
@@ -3123,7 +3123,7 @@
       <c r="E207" s="6"/>
       <c r="F207" s="7"/>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="6"/>
       <c r="B208" s="7"/>
       <c r="C208" s="7"/>
@@ -3131,7 +3131,7 @@
       <c r="E208" s="6"/>
       <c r="F208" s="7"/>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="6"/>
       <c r="B209" s="7"/>
       <c r="C209" s="7"/>
@@ -3139,7 +3139,7 @@
       <c r="E209" s="6"/>
       <c r="F209" s="7"/>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="6"/>
       <c r="B210" s="7"/>
       <c r="C210" s="7"/>
@@ -3147,7 +3147,7 @@
       <c r="E210" s="6"/>
       <c r="F210" s="7"/>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="6"/>
       <c r="B211" s="7"/>
       <c r="C211" s="7"/>
@@ -3155,7 +3155,7 @@
       <c r="E211" s="6"/>
       <c r="F211" s="7"/>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="6"/>
       <c r="B212" s="7"/>
       <c r="C212" s="7"/>
@@ -3163,7 +3163,7 @@
       <c r="E212" s="6"/>
       <c r="F212" s="7"/>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="6"/>
       <c r="B213" s="7"/>
       <c r="C213" s="7"/>
@@ -3171,7 +3171,7 @@
       <c r="E213" s="6"/>
       <c r="F213" s="7"/>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="6"/>
       <c r="B214" s="7"/>
       <c r="C214" s="7"/>
@@ -3179,7 +3179,7 @@
       <c r="E214" s="6"/>
       <c r="F214" s="7"/>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="6"/>
       <c r="B215" s="7"/>
       <c r="C215" s="7"/>
@@ -3187,7 +3187,7 @@
       <c r="E215" s="6"/>
       <c r="F215" s="7"/>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="6"/>
       <c r="B216" s="7"/>
       <c r="C216" s="7"/>
@@ -3195,7 +3195,7 @@
       <c r="E216" s="6"/>
       <c r="F216" s="7"/>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="6"/>
       <c r="B217" s="7"/>
       <c r="C217" s="7"/>
@@ -3203,7 +3203,7 @@
       <c r="E217" s="6"/>
       <c r="F217" s="7"/>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="6"/>
       <c r="B218" s="7"/>
       <c r="C218" s="7"/>
@@ -3211,7 +3211,7 @@
       <c r="E218" s="6"/>
       <c r="F218" s="7"/>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="6"/>
       <c r="B219" s="7"/>
       <c r="C219" s="7"/>
@@ -3219,7 +3219,7 @@
       <c r="E219" s="6"/>
       <c r="F219" s="7"/>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="6"/>
       <c r="B220" s="7"/>
       <c r="C220" s="7"/>
@@ -3227,7 +3227,7 @@
       <c r="E220" s="6"/>
       <c r="F220" s="7"/>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="6"/>
       <c r="B221" s="7"/>
       <c r="C221" s="7"/>
@@ -3235,7 +3235,7 @@
       <c r="E221" s="6"/>
       <c r="F221" s="7"/>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="6"/>
       <c r="B222" s="7"/>
       <c r="C222" s="7"/>
@@ -3243,7 +3243,7 @@
       <c r="E222" s="6"/>
       <c r="F222" s="7"/>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="6"/>
       <c r="B223" s="7"/>
       <c r="C223" s="7"/>
@@ -3251,7 +3251,7 @@
       <c r="E223" s="6"/>
       <c r="F223" s="7"/>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="6"/>
       <c r="B224" s="7"/>
       <c r="C224" s="7"/>
@@ -3259,7 +3259,7 @@
       <c r="E224" s="6"/>
       <c r="F224" s="7"/>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="6"/>
       <c r="B225" s="7"/>
       <c r="C225" s="7"/>
@@ -3267,7 +3267,7 @@
       <c r="E225" s="6"/>
       <c r="F225" s="7"/>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="6"/>
       <c r="B226" s="7"/>
       <c r="C226" s="7"/>
@@ -3275,7 +3275,7 @@
       <c r="E226" s="6"/>
       <c r="F226" s="7"/>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="6"/>
       <c r="B227" s="7"/>
       <c r="C227" s="7"/>
@@ -3283,7 +3283,7 @@
       <c r="E227" s="6"/>
       <c r="F227" s="7"/>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="6"/>
       <c r="B228" s="7"/>
       <c r="C228" s="7"/>
@@ -3291,7 +3291,7 @@
       <c r="E228" s="6"/>
       <c r="F228" s="7"/>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="6"/>
       <c r="B229" s="7"/>
       <c r="C229" s="7"/>
@@ -3299,7 +3299,7 @@
       <c r="E229" s="6"/>
       <c r="F229" s="7"/>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="6"/>
       <c r="B230" s="7"/>
       <c r="C230" s="7"/>
@@ -3307,7 +3307,7 @@
       <c r="E230" s="6"/>
       <c r="F230" s="7"/>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="6"/>
       <c r="B231" s="7"/>
       <c r="C231" s="7"/>
@@ -3315,7 +3315,7 @@
       <c r="E231" s="6"/>
       <c r="F231" s="7"/>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="6"/>
       <c r="B232" s="7"/>
       <c r="C232" s="7"/>
@@ -3323,7 +3323,7 @@
       <c r="E232" s="6"/>
       <c r="F232" s="7"/>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="6"/>
       <c r="B233" s="7"/>
       <c r="C233" s="7"/>
@@ -3331,7 +3331,7 @@
       <c r="E233" s="6"/>
       <c r="F233" s="7"/>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="6"/>
       <c r="B234" s="7"/>
       <c r="C234" s="7"/>
@@ -3339,7 +3339,7 @@
       <c r="E234" s="6"/>
       <c r="F234" s="7"/>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="6"/>
       <c r="B235" s="7"/>
       <c r="C235" s="7"/>
@@ -3347,7 +3347,7 @@
       <c r="E235" s="6"/>
       <c r="F235" s="7"/>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="6"/>
       <c r="B236" s="7"/>
       <c r="C236" s="7"/>
@@ -3355,7 +3355,7 @@
       <c r="E236" s="6"/>
       <c r="F236" s="7"/>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="6"/>
       <c r="B237" s="7"/>
       <c r="C237" s="7"/>
@@ -3363,7 +3363,7 @@
       <c r="E237" s="6"/>
       <c r="F237" s="7"/>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="6"/>
       <c r="B238" s="7"/>
       <c r="C238" s="7"/>
@@ -3371,7 +3371,7 @@
       <c r="E238" s="6"/>
       <c r="F238" s="7"/>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="6"/>
       <c r="B239" s="7"/>
       <c r="C239" s="7"/>
@@ -3379,7 +3379,7 @@
       <c r="E239" s="6"/>
       <c r="F239" s="7"/>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="6"/>
       <c r="B240" s="7"/>
       <c r="C240" s="7"/>
@@ -3387,7 +3387,7 @@
       <c r="E240" s="6"/>
       <c r="F240" s="7"/>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="6"/>
       <c r="B241" s="7"/>
       <c r="C241" s="7"/>
@@ -3395,7 +3395,7 @@
       <c r="E241" s="6"/>
       <c r="F241" s="7"/>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="6"/>
       <c r="B242" s="7"/>
       <c r="C242" s="7"/>
@@ -3403,7 +3403,7 @@
       <c r="E242" s="6"/>
       <c r="F242" s="7"/>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="6"/>
       <c r="B243" s="7"/>
       <c r="C243" s="7"/>
@@ -3411,7 +3411,7 @@
       <c r="E243" s="6"/>
       <c r="F243" s="7"/>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="6"/>
       <c r="B244" s="7"/>
       <c r="C244" s="7"/>
@@ -3419,7 +3419,7 @@
       <c r="E244" s="6"/>
       <c r="F244" s="7"/>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="6"/>
       <c r="B245" s="7"/>
       <c r="C245" s="7"/>
@@ -3427,7 +3427,7 @@
       <c r="E245" s="6"/>
       <c r="F245" s="7"/>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="6"/>
       <c r="B246" s="7"/>
       <c r="C246" s="7"/>
@@ -3435,7 +3435,7 @@
       <c r="E246" s="6"/>
       <c r="F246" s="7"/>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="6"/>
       <c r="B247" s="7"/>
       <c r="C247" s="7"/>
@@ -3443,7 +3443,7 @@
       <c r="E247" s="6"/>
       <c r="F247" s="7"/>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="6"/>
       <c r="B248" s="7"/>
       <c r="C248" s="7"/>
@@ -3451,7 +3451,7 @@
       <c r="E248" s="6"/>
       <c r="F248" s="7"/>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="6"/>
       <c r="B249" s="7"/>
       <c r="C249" s="7"/>
@@ -3459,7 +3459,7 @@
       <c r="E249" s="6"/>
       <c r="F249" s="7"/>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="6"/>
       <c r="B250" s="7"/>
       <c r="C250" s="7"/>
@@ -3467,7 +3467,7 @@
       <c r="E250" s="6"/>
       <c r="F250" s="7"/>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="4"/>
       <c r="B251" s="3"/>
       <c r="C251" s="3"/>
@@ -3475,7 +3475,7 @@
       <c r="E251" s="4"/>
       <c r="F251" s="3"/>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="4"/>
       <c r="B252" s="3"/>
       <c r="C252" s="3"/>
@@ -3483,7 +3483,7 @@
       <c r="E252" s="4"/>
       <c r="F252" s="3"/>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="4"/>
       <c r="B253" s="3"/>
       <c r="C253" s="3"/>
@@ -3491,7 +3491,7 @@
       <c r="E253" s="4"/>
       <c r="F253" s="3"/>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="4"/>
       <c r="B254" s="3"/>
       <c r="C254" s="3"/>
@@ -3499,7 +3499,7 @@
       <c r="E254" s="4"/>
       <c r="F254" s="3"/>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="4"/>
       <c r="B255" s="3"/>
       <c r="C255" s="3"/>
@@ -3507,7 +3507,7 @@
       <c r="E255" s="4"/>
       <c r="F255" s="3"/>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="4"/>
       <c r="B256" s="3"/>
       <c r="C256" s="3"/>
@@ -3515,7 +3515,7 @@
       <c r="E256" s="4"/>
       <c r="F256" s="3"/>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="4"/>
       <c r="B257" s="3"/>
       <c r="C257" s="3"/>
@@ -3523,7 +3523,7 @@
       <c r="E257" s="4"/>
       <c r="F257" s="3"/>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="4"/>
       <c r="B258" s="3"/>
       <c r="C258" s="3"/>
@@ -3531,7 +3531,7 @@
       <c r="E258" s="4"/>
       <c r="F258" s="3"/>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="4"/>
       <c r="B259" s="3"/>
       <c r="C259" s="3"/>
@@ -3539,7 +3539,7 @@
       <c r="E259" s="4"/>
       <c r="F259" s="3"/>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="4"/>
       <c r="B260" s="3"/>
       <c r="C260" s="3"/>
@@ -3547,7 +3547,7 @@
       <c r="E260" s="4"/>
       <c r="F260" s="3"/>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="4"/>
       <c r="B261" s="3"/>
       <c r="C261" s="3"/>
@@ -3555,7 +3555,7 @@
       <c r="E261" s="4"/>
       <c r="F261" s="3"/>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="4"/>
       <c r="B262" s="3"/>
       <c r="C262" s="3"/>
@@ -3563,7 +3563,7 @@
       <c r="E262" s="4"/>
       <c r="F262" s="3"/>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="4"/>
       <c r="B263" s="3"/>
       <c r="C263" s="3"/>
@@ -3571,7 +3571,7 @@
       <c r="E263" s="4"/>
       <c r="F263" s="3"/>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="4"/>
       <c r="B264" s="3"/>
       <c r="C264" s="3"/>
@@ -3579,7 +3579,7 @@
       <c r="E264" s="4"/>
       <c r="F264" s="3"/>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="4"/>
       <c r="B265" s="3"/>
       <c r="C265" s="3"/>
@@ -3587,7 +3587,7 @@
       <c r="E265" s="4"/>
       <c r="F265" s="3"/>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="4"/>
       <c r="B266" s="3"/>
       <c r="C266" s="3"/>
@@ -3595,7 +3595,7 @@
       <c r="E266" s="4"/>
       <c r="F266" s="3"/>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="4"/>
       <c r="B267" s="3"/>
       <c r="C267" s="3"/>
@@ -3603,7 +3603,7 @@
       <c r="E267" s="4"/>
       <c r="F267" s="3"/>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="4"/>
       <c r="B268" s="3"/>
       <c r="C268" s="3"/>
@@ -3611,7 +3611,7 @@
       <c r="E268" s="4"/>
       <c r="F268" s="3"/>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="4"/>
       <c r="B269" s="3"/>
       <c r="C269" s="3"/>
@@ -3619,7 +3619,7 @@
       <c r="E269" s="4"/>
       <c r="F269" s="3"/>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="4"/>
       <c r="B270" s="3"/>
       <c r="C270" s="3"/>
@@ -3627,7 +3627,7 @@
       <c r="E270" s="4"/>
       <c r="F270" s="3"/>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="4"/>
       <c r="B271" s="3"/>
       <c r="C271" s="3"/>
@@ -3635,7 +3635,7 @@
       <c r="E271" s="4"/>
       <c r="F271" s="3"/>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="4"/>
       <c r="B272" s="3"/>
       <c r="C272" s="3"/>
@@ -3643,7 +3643,7 @@
       <c r="E272" s="4"/>
       <c r="F272" s="3"/>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="4"/>
       <c r="B273" s="3"/>
       <c r="C273" s="3"/>
@@ -3651,7 +3651,7 @@
       <c r="E273" s="4"/>
       <c r="F273" s="3"/>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="4"/>
       <c r="B274" s="3"/>
       <c r="C274" s="3"/>
@@ -3659,7 +3659,7 @@
       <c r="E274" s="4"/>
       <c r="F274" s="3"/>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="4"/>
       <c r="B275" s="3"/>
       <c r="C275" s="3"/>
@@ -3667,7 +3667,7 @@
       <c r="E275" s="4"/>
       <c r="F275" s="3"/>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="4"/>
       <c r="B276" s="3"/>
       <c r="C276" s="3"/>
@@ -3675,7 +3675,7 @@
       <c r="E276" s="4"/>
       <c r="F276" s="3"/>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="4"/>
       <c r="B277" s="3"/>
       <c r="C277" s="3"/>
@@ -3683,7 +3683,7 @@
       <c r="E277" s="4"/>
       <c r="F277" s="3"/>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="4"/>
       <c r="B278" s="3"/>
       <c r="C278" s="3"/>
@@ -3691,7 +3691,7 @@
       <c r="E278" s="4"/>
       <c r="F278" s="3"/>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="4"/>
       <c r="B279" s="3"/>
       <c r="C279" s="3"/>
@@ -3699,7 +3699,7 @@
       <c r="E279" s="4"/>
       <c r="F279" s="3"/>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="4"/>
       <c r="B280" s="3"/>
       <c r="C280" s="3"/>
@@ -3707,7 +3707,7 @@
       <c r="E280" s="4"/>
       <c r="F280" s="3"/>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="4"/>
       <c r="B281" s="3"/>
       <c r="C281" s="3"/>
@@ -3715,7 +3715,7 @@
       <c r="E281" s="4"/>
       <c r="F281" s="3"/>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="4"/>
       <c r="B282" s="3"/>
       <c r="C282" s="3"/>
@@ -3723,7 +3723,7 @@
       <c r="E282" s="4"/>
       <c r="F282" s="3"/>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="4"/>
       <c r="B283" s="3"/>
       <c r="C283" s="3"/>
@@ -3731,7 +3731,7 @@
       <c r="E283" s="4"/>
       <c r="F283" s="3"/>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="4"/>
       <c r="B284" s="3"/>
       <c r="C284" s="3"/>
@@ -3739,7 +3739,7 @@
       <c r="E284" s="4"/>
       <c r="F284" s="3"/>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="4"/>
       <c r="B285" s="3"/>
       <c r="C285" s="3"/>
@@ -3747,7 +3747,7 @@
       <c r="E285" s="4"/>
       <c r="F285" s="3"/>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="4"/>
       <c r="B286" s="3"/>
       <c r="C286" s="3"/>
@@ -3755,7 +3755,7 @@
       <c r="E286" s="4"/>
       <c r="F286" s="3"/>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="4"/>
       <c r="B287" s="3"/>
       <c r="C287" s="3"/>
@@ -3763,7 +3763,7 @@
       <c r="E287" s="4"/>
       <c r="F287" s="3"/>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="4"/>
       <c r="B288" s="3"/>
       <c r="C288" s="3"/>
@@ -3771,7 +3771,7 @@
       <c r="E288" s="4"/>
       <c r="F288" s="3"/>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="4"/>
       <c r="B289" s="3"/>
       <c r="C289" s="3"/>
@@ -3779,7 +3779,7 @@
       <c r="E289" s="4"/>
       <c r="F289" s="3"/>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="4"/>
       <c r="B290" s="3"/>
       <c r="C290" s="3"/>
@@ -3787,7 +3787,7 @@
       <c r="E290" s="4"/>
       <c r="F290" s="3"/>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="4"/>
       <c r="B291" s="3"/>
       <c r="C291" s="3"/>
@@ -3795,7 +3795,7 @@
       <c r="E291" s="4"/>
       <c r="F291" s="3"/>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="4"/>
       <c r="B292" s="3"/>
       <c r="C292" s="3"/>
@@ -3803,7 +3803,7 @@
       <c r="E292" s="4"/>
       <c r="F292" s="3"/>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="4"/>
       <c r="B293" s="3"/>
       <c r="C293" s="3"/>
@@ -3811,7 +3811,7 @@
       <c r="E293" s="4"/>
       <c r="F293" s="3"/>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="4"/>
       <c r="B294" s="3"/>
       <c r="C294" s="3"/>
@@ -3819,7 +3819,7 @@
       <c r="E294" s="4"/>
       <c r="F294" s="3"/>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="4"/>
       <c r="B295" s="3"/>
       <c r="C295" s="3"/>
@@ -3827,7 +3827,7 @@
       <c r="E295" s="4"/>
       <c r="F295" s="3"/>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="4"/>
       <c r="B296" s="3"/>
       <c r="C296" s="3"/>
@@ -3835,7 +3835,7 @@
       <c r="E296" s="4"/>
       <c r="F296" s="3"/>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="4"/>
       <c r="B297" s="3"/>
       <c r="C297" s="3"/>
@@ -3843,7 +3843,7 @@
       <c r="E297" s="4"/>
       <c r="F297" s="3"/>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="4"/>
       <c r="B298" s="3"/>
       <c r="C298" s="3"/>
@@ -3851,7 +3851,7 @@
       <c r="E298" s="4"/>
       <c r="F298" s="3"/>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="4"/>
       <c r="B299" s="3"/>
       <c r="C299" s="3"/>
@@ -3859,7 +3859,7 @@
       <c r="E299" s="4"/>
       <c r="F299" s="3"/>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="4"/>
       <c r="B300" s="3"/>
       <c r="C300" s="3"/>
@@ -3867,7 +3867,7 @@
       <c r="E300" s="4"/>
       <c r="F300" s="3"/>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="4"/>
       <c r="B301" s="3"/>
       <c r="C301" s="3"/>
@@ -3875,7 +3875,7 @@
       <c r="E301" s="4"/>
       <c r="F301" s="3"/>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="4"/>
       <c r="B302" s="3"/>
       <c r="C302" s="3"/>
@@ -3883,7 +3883,7 @@
       <c r="E302" s="4"/>
       <c r="F302" s="3"/>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" s="4"/>
       <c r="B303" s="3"/>
       <c r="C303" s="3"/>
@@ -3891,7 +3891,7 @@
       <c r="E303" s="4"/>
       <c r="F303" s="3"/>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" s="4"/>
       <c r="B304" s="3"/>
       <c r="C304" s="3"/>
@@ -3899,7 +3899,7 @@
       <c r="E304" s="4"/>
       <c r="F304" s="3"/>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" s="4"/>
       <c r="B305" s="3"/>
       <c r="C305" s="3"/>
@@ -3907,7 +3907,7 @@
       <c r="E305" s="4"/>
       <c r="F305" s="3"/>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" s="4"/>
       <c r="B306" s="3"/>
       <c r="C306" s="3"/>
@@ -3915,7 +3915,7 @@
       <c r="E306" s="4"/>
       <c r="F306" s="3"/>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" s="4"/>
       <c r="B307" s="3"/>
       <c r="C307" s="3"/>
@@ -3923,7 +3923,7 @@
       <c r="E307" s="4"/>
       <c r="F307" s="3"/>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" s="4"/>
       <c r="B308" s="3"/>
       <c r="C308" s="3"/>
@@ -3931,7 +3931,7 @@
       <c r="E308" s="4"/>
       <c r="F308" s="3"/>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" s="4"/>
       <c r="B309" s="3"/>
       <c r="C309" s="3"/>
@@ -3939,7 +3939,7 @@
       <c r="E309" s="4"/>
       <c r="F309" s="3"/>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" s="4"/>
       <c r="B310" s="3"/>
       <c r="C310" s="3"/>
@@ -3947,7 +3947,7 @@
       <c r="E310" s="4"/>
       <c r="F310" s="3"/>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" s="4"/>
       <c r="B311" s="3"/>
       <c r="C311" s="3"/>
@@ -3955,7 +3955,7 @@
       <c r="E311" s="4"/>
       <c r="F311" s="3"/>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" s="4"/>
       <c r="B312" s="3"/>
       <c r="C312" s="3"/>
@@ -3963,7 +3963,7 @@
       <c r="E312" s="4"/>
       <c r="F312" s="3"/>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" s="4"/>
       <c r="B313" s="3"/>
       <c r="C313" s="3"/>
@@ -3971,7 +3971,7 @@
       <c r="E313" s="4"/>
       <c r="F313" s="3"/>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" s="4"/>
       <c r="B314" s="3"/>
       <c r="C314" s="3"/>
@@ -3979,7 +3979,7 @@
       <c r="E314" s="4"/>
       <c r="F314" s="3"/>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" s="4"/>
       <c r="B315" s="3"/>
       <c r="C315" s="3"/>
@@ -3987,7 +3987,7 @@
       <c r="E315" s="4"/>
       <c r="F315" s="3"/>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="4"/>
       <c r="B316" s="3"/>
       <c r="C316" s="3"/>
@@ -3995,7 +3995,7 @@
       <c r="E316" s="4"/>
       <c r="F316" s="3"/>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" s="4"/>
       <c r="B317" s="3"/>
       <c r="C317" s="3"/>
@@ -4003,7 +4003,7 @@
       <c r="E317" s="4"/>
       <c r="F317" s="3"/>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" s="4"/>
       <c r="B318" s="3"/>
       <c r="C318" s="3"/>
@@ -4011,7 +4011,7 @@
       <c r="E318" s="4"/>
       <c r="F318" s="3"/>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" s="4"/>
       <c r="B319" s="3"/>
       <c r="C319" s="3"/>
@@ -4019,7 +4019,7 @@
       <c r="E319" s="4"/>
       <c r="F319" s="3"/>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" s="4"/>
       <c r="B320" s="3"/>
       <c r="C320" s="3"/>
@@ -4027,7 +4027,7 @@
       <c r="E320" s="4"/>
       <c r="F320" s="3"/>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" s="4"/>
       <c r="B321" s="3"/>
       <c r="C321" s="3"/>
@@ -4035,7 +4035,7 @@
       <c r="E321" s="4"/>
       <c r="F321" s="3"/>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" s="4"/>
       <c r="B322" s="3"/>
       <c r="C322" s="3"/>
@@ -4043,7 +4043,7 @@
       <c r="E322" s="4"/>
       <c r="F322" s="3"/>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" s="4"/>
       <c r="B323" s="3"/>
       <c r="C323" s="3"/>
@@ -4051,7 +4051,7 @@
       <c r="E323" s="4"/>
       <c r="F323" s="3"/>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" s="4"/>
       <c r="B324" s="3"/>
       <c r="C324" s="3"/>
@@ -4059,7 +4059,7 @@
       <c r="E324" s="4"/>
       <c r="F324" s="3"/>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" s="4"/>
       <c r="B325" s="3"/>
       <c r="C325" s="3"/>
@@ -4067,7 +4067,7 @@
       <c r="E325" s="4"/>
       <c r="F325" s="3"/>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" s="4"/>
       <c r="B326" s="3"/>
       <c r="C326" s="3"/>
@@ -4075,7 +4075,7 @@
       <c r="E326" s="4"/>
       <c r="F326" s="3"/>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" s="4"/>
       <c r="B327" s="3"/>
       <c r="C327" s="3"/>
@@ -4083,7 +4083,7 @@
       <c r="E327" s="4"/>
       <c r="F327" s="3"/>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="4"/>
       <c r="B328" s="3"/>
       <c r="C328" s="3"/>
@@ -4091,7 +4091,7 @@
       <c r="E328" s="4"/>
       <c r="F328" s="3"/>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" s="4"/>
       <c r="B329" s="3"/>
       <c r="C329" s="3"/>
@@ -4099,7 +4099,7 @@
       <c r="E329" s="4"/>
       <c r="F329" s="3"/>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" s="4"/>
       <c r="B330" s="3"/>
       <c r="C330" s="3"/>
@@ -4107,7 +4107,7 @@
       <c r="E330" s="4"/>
       <c r="F330" s="3"/>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" s="4"/>
       <c r="B331" s="3"/>
       <c r="C331" s="3"/>
@@ -4115,7 +4115,7 @@
       <c r="E331" s="4"/>
       <c r="F331" s="3"/>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" s="4"/>
       <c r="B332" s="3"/>
       <c r="C332" s="3"/>
@@ -4123,7 +4123,7 @@
       <c r="E332" s="4"/>
       <c r="F332" s="3"/>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" s="4"/>
       <c r="B333" s="3"/>
       <c r="C333" s="3"/>
@@ -4131,7 +4131,7 @@
       <c r="E333" s="4"/>
       <c r="F333" s="3"/>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" s="4"/>
       <c r="B334" s="3"/>
       <c r="C334" s="3"/>
@@ -4139,7 +4139,7 @@
       <c r="E334" s="4"/>
       <c r="F334" s="3"/>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" s="4"/>
       <c r="B335" s="3"/>
       <c r="C335" s="3"/>
@@ -4147,7 +4147,7 @@
       <c r="E335" s="4"/>
       <c r="F335" s="3"/>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" s="4"/>
       <c r="B336" s="3"/>
       <c r="C336" s="3"/>
@@ -4155,7 +4155,7 @@
       <c r="E336" s="4"/>
       <c r="F336" s="3"/>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" s="4"/>
       <c r="B337" s="3"/>
       <c r="C337" s="3"/>
@@ -4163,7 +4163,7 @@
       <c r="E337" s="4"/>
       <c r="F337" s="3"/>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="4"/>
       <c r="B338" s="3"/>
       <c r="C338" s="3"/>
@@ -4171,7 +4171,7 @@
       <c r="E338" s="4"/>
       <c r="F338" s="3"/>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" s="4"/>
       <c r="B339" s="3"/>
       <c r="C339" s="3"/>
@@ -4179,7 +4179,7 @@
       <c r="E339" s="4"/>
       <c r="F339" s="3"/>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" s="4"/>
       <c r="B340" s="3"/>
       <c r="C340" s="3"/>
@@ -4187,7 +4187,7 @@
       <c r="E340" s="4"/>
       <c r="F340" s="3"/>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" s="4"/>
       <c r="B341" s="3"/>
       <c r="C341" s="3"/>
@@ -4195,7 +4195,7 @@
       <c r="E341" s="4"/>
       <c r="F341" s="3"/>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A342" s="4"/>
       <c r="B342" s="3"/>
       <c r="C342" s="3"/>
@@ -4203,7 +4203,7 @@
       <c r="E342" s="4"/>
       <c r="F342" s="3"/>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A343" s="4"/>
       <c r="B343" s="3"/>
       <c r="C343" s="3"/>
@@ -4211,7 +4211,7 @@
       <c r="E343" s="4"/>
       <c r="F343" s="3"/>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" s="4"/>
       <c r="B344" s="3"/>
       <c r="C344" s="3"/>
@@ -4219,7 +4219,7 @@
       <c r="E344" s="4"/>
       <c r="F344" s="3"/>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" s="4"/>
       <c r="B345" s="3"/>
       <c r="C345" s="3"/>
@@ -4227,7 +4227,7 @@
       <c r="E345" s="4"/>
       <c r="F345" s="3"/>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" s="4"/>
       <c r="B346" s="3"/>
       <c r="C346" s="3"/>
@@ -4235,7 +4235,7 @@
       <c r="E346" s="4"/>
       <c r="F346" s="3"/>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" s="4"/>
       <c r="B347" s="3"/>
       <c r="C347" s="3"/>
@@ -4243,7 +4243,7 @@
       <c r="E347" s="4"/>
       <c r="F347" s="3"/>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" s="4"/>
       <c r="B348" s="3"/>
       <c r="C348" s="3"/>
@@ -4251,7 +4251,7 @@
       <c r="E348" s="4"/>
       <c r="F348" s="3"/>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" s="4"/>
       <c r="B349" s="3"/>
       <c r="C349" s="3"/>
@@ -4259,7 +4259,7 @@
       <c r="E349" s="4"/>
       <c r="F349" s="3"/>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" s="4"/>
       <c r="B350" s="3"/>
       <c r="C350" s="3"/>
@@ -4267,7 +4267,7 @@
       <c r="E350" s="4"/>
       <c r="F350" s="3"/>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" s="4"/>
       <c r="B351" s="3"/>
       <c r="C351" s="3"/>
@@ -4275,7 +4275,7 @@
       <c r="E351" s="4"/>
       <c r="F351" s="3"/>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="4"/>
       <c r="B352" s="3"/>
       <c r="C352" s="3"/>
@@ -4283,7 +4283,7 @@
       <c r="E352" s="4"/>
       <c r="F352" s="3"/>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" s="4"/>
       <c r="B353" s="3"/>
       <c r="C353" s="3"/>
@@ -4291,7 +4291,7 @@
       <c r="E353" s="4"/>
       <c r="F353" s="3"/>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" s="4"/>
       <c r="B354" s="3"/>
       <c r="C354" s="3"/>
@@ -4299,7 +4299,7 @@
       <c r="E354" s="4"/>
       <c r="F354" s="3"/>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" s="4"/>
       <c r="B355" s="3"/>
       <c r="C355" s="3"/>
@@ -4307,7 +4307,7 @@
       <c r="E355" s="4"/>
       <c r="F355" s="3"/>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A356" s="4"/>
       <c r="B356" s="3"/>
       <c r="C356" s="3"/>
@@ -4315,7 +4315,7 @@
       <c r="E356" s="4"/>
       <c r="F356" s="3"/>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A357" s="4"/>
       <c r="B357" s="3"/>
       <c r="C357" s="3"/>
@@ -4323,7 +4323,7 @@
       <c r="E357" s="4"/>
       <c r="F357" s="3"/>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A358" s="4"/>
       <c r="B358" s="3"/>
       <c r="C358" s="3"/>
@@ -4331,7 +4331,7 @@
       <c r="E358" s="4"/>
       <c r="F358" s="3"/>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A359" s="4"/>
       <c r="B359" s="3"/>
       <c r="C359" s="3"/>
@@ -4339,7 +4339,7 @@
       <c r="E359" s="4"/>
       <c r="F359" s="3"/>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A360" s="4"/>
       <c r="B360" s="3"/>
       <c r="C360" s="3"/>
@@ -4347,7 +4347,7 @@
       <c r="E360" s="4"/>
       <c r="F360" s="3"/>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A361" s="4"/>
       <c r="B361" s="3"/>
       <c r="C361" s="3"/>
@@ -4355,7 +4355,7 @@
       <c r="E361" s="4"/>
       <c r="F361" s="3"/>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A362" s="4"/>
       <c r="B362" s="3"/>
       <c r="C362" s="3"/>
@@ -4363,7 +4363,7 @@
       <c r="E362" s="4"/>
       <c r="F362" s="3"/>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A363" s="4"/>
       <c r="B363" s="3"/>
       <c r="C363" s="3"/>
@@ -4371,7 +4371,7 @@
       <c r="E363" s="4"/>
       <c r="F363" s="3"/>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A364" s="4"/>
       <c r="B364" s="3"/>
       <c r="C364" s="3"/>
@@ -4379,7 +4379,7 @@
       <c r="E364" s="4"/>
       <c r="F364" s="3"/>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A365" s="4"/>
       <c r="B365" s="3"/>
       <c r="C365" s="3"/>
@@ -4387,7 +4387,7 @@
       <c r="E365" s="4"/>
       <c r="F365" s="3"/>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A366" s="4"/>
       <c r="B366" s="3"/>
       <c r="C366" s="3"/>
@@ -4395,7 +4395,7 @@
       <c r="E366" s="4"/>
       <c r="F366" s="3"/>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A367" s="4"/>
       <c r="B367" s="3"/>
       <c r="C367" s="3"/>
@@ -4403,7 +4403,7 @@
       <c r="E367" s="4"/>
       <c r="F367" s="3"/>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A368" s="4"/>
       <c r="B368" s="3"/>
       <c r="C368" s="3"/>
@@ -4411,7 +4411,7 @@
       <c r="E368" s="4"/>
       <c r="F368" s="3"/>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A369" s="4"/>
       <c r="B369" s="3"/>
       <c r="C369" s="3"/>
@@ -4419,7 +4419,7 @@
       <c r="E369" s="4"/>
       <c r="F369" s="3"/>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A370" s="4"/>
       <c r="B370" s="3"/>
       <c r="C370" s="3"/>
@@ -4427,7 +4427,7 @@
       <c r="E370" s="4"/>
       <c r="F370" s="3"/>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A371" s="4"/>
       <c r="B371" s="3"/>
       <c r="C371" s="3"/>
@@ -4435,7 +4435,7 @@
       <c r="E371" s="4"/>
       <c r="F371" s="3"/>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A372" s="4"/>
       <c r="B372" s="3"/>
       <c r="C372" s="3"/>
@@ -4443,7 +4443,7 @@
       <c r="E372" s="4"/>
       <c r="F372" s="3"/>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A373" s="4"/>
       <c r="B373" s="3"/>
       <c r="C373" s="3"/>
@@ -4451,7 +4451,7 @@
       <c r="E373" s="4"/>
       <c r="F373" s="3"/>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A374" s="4"/>
       <c r="B374" s="3"/>
       <c r="C374" s="3"/>
@@ -4459,7 +4459,7 @@
       <c r="E374" s="4"/>
       <c r="F374" s="3"/>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A375" s="4"/>
       <c r="B375" s="3"/>
       <c r="C375" s="3"/>
@@ -4467,7 +4467,7 @@
       <c r="E375" s="4"/>
       <c r="F375" s="3"/>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A376" s="4"/>
       <c r="B376" s="3"/>
       <c r="C376" s="3"/>
@@ -4475,7 +4475,7 @@
       <c r="E376" s="4"/>
       <c r="F376" s="3"/>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A377" s="4"/>
       <c r="B377" s="3"/>
       <c r="C377" s="3"/>
@@ -4483,7 +4483,7 @@
       <c r="E377" s="4"/>
       <c r="F377" s="3"/>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A378" s="4"/>
       <c r="B378" s="3"/>
       <c r="C378" s="3"/>
@@ -4491,7 +4491,7 @@
       <c r="E378" s="4"/>
       <c r="F378" s="3"/>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A379" s="4"/>
       <c r="B379" s="3"/>
       <c r="C379" s="3"/>
@@ -4499,7 +4499,7 @@
       <c r="E379" s="4"/>
       <c r="F379" s="3"/>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A380" s="4"/>
       <c r="B380" s="3"/>
       <c r="C380" s="3"/>
@@ -4507,7 +4507,7 @@
       <c r="E380" s="4"/>
       <c r="F380" s="3"/>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A381" s="4"/>
       <c r="B381" s="3"/>
       <c r="C381" s="3"/>
@@ -4515,7 +4515,7 @@
       <c r="E381" s="4"/>
       <c r="F381" s="3"/>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A382" s="4"/>
       <c r="B382" s="3"/>
       <c r="C382" s="3"/>
@@ -4523,7 +4523,7 @@
       <c r="E382" s="4"/>
       <c r="F382" s="3"/>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A383" s="4"/>
       <c r="B383" s="3"/>
       <c r="C383" s="3"/>
@@ -4531,7 +4531,7 @@
       <c r="E383" s="4"/>
       <c r="F383" s="3"/>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A384" s="4"/>
       <c r="B384" s="3"/>
       <c r="C384" s="3"/>
@@ -4539,7 +4539,7 @@
       <c r="E384" s="4"/>
       <c r="F384" s="3"/>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A385" s="4"/>
       <c r="B385" s="3"/>
       <c r="C385" s="3"/>
@@ -4547,7 +4547,7 @@
       <c r="E385" s="4"/>
       <c r="F385" s="3"/>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A386" s="4"/>
       <c r="B386" s="3"/>
       <c r="C386" s="3"/>
@@ -4555,7 +4555,7 @@
       <c r="E386" s="4"/>
       <c r="F386" s="3"/>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A387" s="4"/>
       <c r="B387" s="3"/>
       <c r="C387" s="3"/>
@@ -4563,7 +4563,7 @@
       <c r="E387" s="4"/>
       <c r="F387" s="3"/>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A388" s="4"/>
       <c r="B388" s="3"/>
       <c r="C388" s="3"/>
@@ -4571,7 +4571,7 @@
       <c r="E388" s="4"/>
       <c r="F388" s="3"/>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A389" s="4"/>
       <c r="B389" s="3"/>
       <c r="C389" s="3"/>
@@ -4579,7 +4579,7 @@
       <c r="E389" s="4"/>
       <c r="F389" s="3"/>
     </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A390" s="4"/>
       <c r="B390" s="3"/>
       <c r="C390" s="3"/>
@@ -4587,7 +4587,7 @@
       <c r="E390" s="4"/>
       <c r="F390" s="3"/>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A391" s="4"/>
       <c r="B391" s="3"/>
       <c r="C391" s="3"/>
@@ -4595,7 +4595,7 @@
       <c r="E391" s="4"/>
       <c r="F391" s="3"/>
     </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A392" s="4"/>
       <c r="B392" s="3"/>
       <c r="C392" s="3"/>
@@ -4603,7 +4603,7 @@
       <c r="E392" s="4"/>
       <c r="F392" s="3"/>
     </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A393" s="4"/>
       <c r="B393" s="3"/>
       <c r="C393" s="3"/>
@@ -4611,7 +4611,7 @@
       <c r="E393" s="4"/>
       <c r="F393" s="3"/>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A394" s="4"/>
       <c r="B394" s="3"/>
       <c r="C394" s="3"/>
@@ -4619,7 +4619,7 @@
       <c r="E394" s="4"/>
       <c r="F394" s="3"/>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A395" s="4"/>
       <c r="B395" s="3"/>
       <c r="C395" s="3"/>
@@ -4627,7 +4627,7 @@
       <c r="E395" s="4"/>
       <c r="F395" s="3"/>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A396" s="4"/>
       <c r="B396" s="3"/>
       <c r="C396" s="3"/>
@@ -4635,7 +4635,7 @@
       <c r="E396" s="4"/>
       <c r="F396" s="3"/>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A397" s="4"/>
       <c r="B397" s="3"/>
       <c r="C397" s="3"/>
@@ -4643,7 +4643,7 @@
       <c r="E397" s="4"/>
       <c r="F397" s="3"/>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A398" s="4"/>
       <c r="B398" s="3"/>
       <c r="C398" s="3"/>
@@ -4651,7 +4651,7 @@
       <c r="E398" s="4"/>
       <c r="F398" s="3"/>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A399" s="4"/>
       <c r="B399" s="3"/>
       <c r="C399" s="3"/>
@@ -4659,7 +4659,7 @@
       <c r="E399" s="4"/>
       <c r="F399" s="3"/>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A400" s="4"/>
       <c r="B400" s="3"/>
       <c r="C400" s="3"/>
@@ -4667,7 +4667,7 @@
       <c r="E400" s="4"/>
       <c r="F400" s="3"/>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A401" s="4"/>
       <c r="B401" s="3"/>
       <c r="C401" s="3"/>
@@ -4675,7 +4675,7 @@
       <c r="E401" s="4"/>
       <c r="F401" s="3"/>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A402" s="4"/>
       <c r="B402" s="3"/>
       <c r="C402" s="3"/>
@@ -4683,7 +4683,7 @@
       <c r="E402" s="4"/>
       <c r="F402" s="3"/>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A403" s="4"/>
       <c r="B403" s="3"/>
       <c r="C403" s="3"/>
@@ -4691,7 +4691,7 @@
       <c r="E403" s="4"/>
       <c r="F403" s="3"/>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A404" s="4"/>
       <c r="B404" s="3"/>
       <c r="C404" s="3"/>
@@ -4699,7 +4699,7 @@
       <c r="E404" s="4"/>
       <c r="F404" s="3"/>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A405" s="4"/>
       <c r="B405" s="3"/>
       <c r="C405" s="3"/>
@@ -4707,7 +4707,7 @@
       <c r="E405" s="4"/>
       <c r="F405" s="3"/>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A406" s="4"/>
       <c r="B406" s="3"/>
       <c r="C406" s="3"/>
@@ -4715,7 +4715,7 @@
       <c r="E406" s="4"/>
       <c r="F406" s="3"/>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A407" s="4"/>
       <c r="B407" s="3"/>
       <c r="C407" s="3"/>
@@ -4723,7 +4723,7 @@
       <c r="E407" s="4"/>
       <c r="F407" s="3"/>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A408" s="4"/>
       <c r="B408" s="3"/>
       <c r="C408" s="3"/>
@@ -4731,7 +4731,7 @@
       <c r="E408" s="4"/>
       <c r="F408" s="3"/>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A409" s="4"/>
       <c r="B409" s="3"/>
       <c r="C409" s="3"/>
@@ -4739,7 +4739,7 @@
       <c r="E409" s="4"/>
       <c r="F409" s="3"/>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A410" s="4"/>
       <c r="B410" s="3"/>
       <c r="C410" s="3"/>
@@ -4747,7 +4747,7 @@
       <c r="E410" s="4"/>
       <c r="F410" s="3"/>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A411" s="4"/>
       <c r="B411" s="3"/>
       <c r="C411" s="3"/>
@@ -4755,7 +4755,7 @@
       <c r="E411" s="4"/>
       <c r="F411" s="3"/>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A412" s="4"/>
       <c r="B412" s="3"/>
       <c r="C412" s="3"/>
@@ -4763,7 +4763,7 @@
       <c r="E412" s="4"/>
       <c r="F412" s="3"/>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A413" s="4"/>
       <c r="B413" s="3"/>
       <c r="C413" s="3"/>
@@ -4771,7 +4771,7 @@
       <c r="E413" s="4"/>
       <c r="F413" s="3"/>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A414" s="4"/>
       <c r="B414" s="3"/>
       <c r="C414" s="3"/>
@@ -4779,7 +4779,7 @@
       <c r="E414" s="4"/>
       <c r="F414" s="3"/>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A415" s="4"/>
       <c r="B415" s="3"/>
       <c r="C415" s="3"/>
@@ -4787,7 +4787,7 @@
       <c r="E415" s="4"/>
       <c r="F415" s="3"/>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A416" s="4"/>
       <c r="B416" s="3"/>
       <c r="C416" s="3"/>
@@ -4795,7 +4795,7 @@
       <c r="E416" s="4"/>
       <c r="F416" s="3"/>
     </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A417" s="4"/>
       <c r="B417" s="3"/>
       <c r="C417" s="3"/>
@@ -4803,7 +4803,7 @@
       <c r="E417" s="4"/>
       <c r="F417" s="3"/>
     </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A418" s="4"/>
       <c r="B418" s="3"/>
       <c r="C418" s="3"/>
@@ -4811,7 +4811,7 @@
       <c r="E418" s="4"/>
       <c r="F418" s="3"/>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A419" s="4"/>
       <c r="B419" s="3"/>
       <c r="C419" s="3"/>
@@ -4819,7 +4819,7 @@
       <c r="E419" s="4"/>
       <c r="F419" s="3"/>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A420" s="4"/>
       <c r="B420" s="3"/>
       <c r="C420" s="3"/>
@@ -4827,7 +4827,7 @@
       <c r="E420" s="4"/>
       <c r="F420" s="3"/>
     </row>
-    <row r="421" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A421" s="4"/>
       <c r="B421" s="3"/>
       <c r="C421" s="3"/>
@@ -4835,7 +4835,7 @@
       <c r="E421" s="4"/>
       <c r="F421" s="3"/>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A422" s="4"/>
       <c r="B422" s="3"/>
       <c r="C422" s="3"/>
@@ -4843,7 +4843,7 @@
       <c r="E422" s="4"/>
       <c r="F422" s="3"/>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A423" s="4"/>
       <c r="B423" s="3"/>
       <c r="C423" s="3"/>
@@ -4851,7 +4851,7 @@
       <c r="E423" s="4"/>
       <c r="F423" s="3"/>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A424" s="4"/>
       <c r="B424" s="3"/>
       <c r="C424" s="3"/>
@@ -4859,7 +4859,7 @@
       <c r="E424" s="4"/>
       <c r="F424" s="3"/>
     </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A425" s="4"/>
       <c r="B425" s="3"/>
       <c r="C425" s="3"/>
@@ -4867,7 +4867,7 @@
       <c r="E425" s="4"/>
       <c r="F425" s="3"/>
     </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A426" s="4"/>
       <c r="B426" s="3"/>
       <c r="C426" s="3"/>
@@ -4875,7 +4875,7 @@
       <c r="E426" s="4"/>
       <c r="F426" s="3"/>
     </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A427" s="4"/>
       <c r="B427" s="3"/>
       <c r="C427" s="3"/>
@@ -4883,7 +4883,7 @@
       <c r="E427" s="4"/>
       <c r="F427" s="3"/>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A428" s="4"/>
       <c r="B428" s="3"/>
       <c r="C428" s="3"/>
@@ -4891,7 +4891,7 @@
       <c r="E428" s="4"/>
       <c r="F428" s="3"/>
     </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A429" s="4"/>
       <c r="B429" s="3"/>
       <c r="C429" s="3"/>
@@ -4899,7 +4899,7 @@
       <c r="E429" s="4"/>
       <c r="F429" s="3"/>
     </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A430" s="4"/>
       <c r="B430" s="3"/>
       <c r="C430" s="3"/>
@@ -4907,7 +4907,7 @@
       <c r="E430" s="4"/>
       <c r="F430" s="3"/>
     </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A431" s="4"/>
       <c r="B431" s="3"/>
       <c r="C431" s="3"/>
@@ -4915,7 +4915,7 @@
       <c r="E431" s="4"/>
       <c r="F431" s="3"/>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A432" s="4"/>
       <c r="B432" s="3"/>
       <c r="C432" s="3"/>
@@ -4923,7 +4923,7 @@
       <c r="E432" s="4"/>
       <c r="F432" s="3"/>
     </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A433" s="4"/>
       <c r="B433" s="3"/>
       <c r="C433" s="3"/>
@@ -4931,7 +4931,7 @@
       <c r="E433" s="4"/>
       <c r="F433" s="3"/>
     </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A434" s="4"/>
       <c r="B434" s="3"/>
       <c r="C434" s="3"/>
@@ -4939,7 +4939,7 @@
       <c r="E434" s="4"/>
       <c r="F434" s="3"/>
     </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A435" s="4"/>
       <c r="B435" s="3"/>
       <c r="C435" s="3"/>
@@ -4947,7 +4947,7 @@
       <c r="E435" s="4"/>
       <c r="F435" s="3"/>
     </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A436" s="4"/>
       <c r="B436" s="3"/>
       <c r="C436" s="3"/>
@@ -4955,7 +4955,7 @@
       <c r="E436" s="4"/>
       <c r="F436" s="3"/>
     </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A437" s="4"/>
       <c r="B437" s="3"/>
       <c r="C437" s="3"/>
@@ -4963,7 +4963,7 @@
       <c r="E437" s="4"/>
       <c r="F437" s="3"/>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A438" s="4"/>
       <c r="B438" s="3"/>
       <c r="C438" s="3"/>
@@ -4971,7 +4971,7 @@
       <c r="E438" s="4"/>
       <c r="F438" s="3"/>
     </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A439" s="4"/>
       <c r="B439" s="3"/>
       <c r="C439" s="3"/>
@@ -4979,7 +4979,7 @@
       <c r="E439" s="4"/>
       <c r="F439" s="3"/>
     </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A440" s="4"/>
       <c r="B440" s="3"/>
       <c r="C440" s="3"/>
@@ -4987,7 +4987,7 @@
       <c r="E440" s="4"/>
       <c r="F440" s="3"/>
     </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A441" s="4"/>
       <c r="B441" s="3"/>
       <c r="C441" s="3"/>
@@ -4995,7 +4995,7 @@
       <c r="E441" s="4"/>
       <c r="F441" s="3"/>
     </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A442" s="4"/>
       <c r="B442" s="3"/>
       <c r="C442" s="3"/>
@@ -5003,7 +5003,7 @@
       <c r="E442" s="4"/>
       <c r="F442" s="3"/>
     </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A443" s="4"/>
       <c r="B443" s="3"/>
       <c r="C443" s="3"/>
@@ -5011,7 +5011,7 @@
       <c r="E443" s="4"/>
       <c r="F443" s="3"/>
     </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A444" s="4"/>
       <c r="B444" s="3"/>
       <c r="C444" s="3"/>
@@ -5019,7 +5019,7 @@
       <c r="E444" s="4"/>
       <c r="F444" s="3"/>
     </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A445" s="4"/>
       <c r="B445" s="3"/>
       <c r="C445" s="3"/>
@@ -5027,7 +5027,7 @@
       <c r="E445" s="4"/>
       <c r="F445" s="3"/>
     </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A446" s="4"/>
       <c r="B446" s="3"/>
       <c r="C446" s="3"/>
@@ -5035,7 +5035,7 @@
       <c r="E446" s="4"/>
       <c r="F446" s="3"/>
     </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A447" s="4"/>
       <c r="B447" s="3"/>
       <c r="C447" s="3"/>
@@ -5043,7 +5043,7 @@
       <c r="E447" s="4"/>
       <c r="F447" s="3"/>
     </row>
-    <row r="448" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A448" s="4"/>
       <c r="B448" s="3"/>
       <c r="C448" s="3"/>
@@ -5051,7 +5051,7 @@
       <c r="E448" s="4"/>
       <c r="F448" s="3"/>
     </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A449" s="4"/>
       <c r="B449" s="3"/>
       <c r="C449" s="3"/>
@@ -5059,7 +5059,7 @@
       <c r="E449" s="4"/>
       <c r="F449" s="3"/>
     </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A450" s="4"/>
       <c r="B450" s="3"/>
       <c r="C450" s="3"/>
@@ -5067,7 +5067,7 @@
       <c r="E450" s="4"/>
       <c r="F450" s="3"/>
     </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A451" s="4"/>
       <c r="B451" s="3"/>
       <c r="C451" s="3"/>
@@ -5075,7 +5075,7 @@
       <c r="E451" s="4"/>
       <c r="F451" s="3"/>
     </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A452" s="4"/>
       <c r="B452" s="3"/>
       <c r="C452" s="3"/>
@@ -5083,7 +5083,7 @@
       <c r="E452" s="4"/>
       <c r="F452" s="3"/>
     </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A453" s="4"/>
       <c r="B453" s="3"/>
       <c r="C453" s="3"/>
@@ -5091,7 +5091,7 @@
       <c r="E453" s="4"/>
       <c r="F453" s="3"/>
     </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A454" s="4"/>
       <c r="B454" s="3"/>
       <c r="C454" s="3"/>
@@ -5099,7 +5099,7 @@
       <c r="E454" s="4"/>
       <c r="F454" s="3"/>
     </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A455" s="4"/>
       <c r="B455" s="3"/>
       <c r="C455" s="3"/>
@@ -5107,7 +5107,7 @@
       <c r="E455" s="4"/>
       <c r="F455" s="3"/>
     </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A456" s="4"/>
       <c r="B456" s="3"/>
       <c r="C456" s="3"/>
@@ -5115,7 +5115,7 @@
       <c r="E456" s="4"/>
       <c r="F456" s="3"/>
     </row>
-    <row r="457" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A457" s="4"/>
       <c r="B457" s="3"/>
       <c r="C457" s="3"/>
@@ -5123,7 +5123,7 @@
       <c r="E457" s="4"/>
       <c r="F457" s="3"/>
     </row>
-    <row r="458" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A458" s="4"/>
       <c r="B458" s="3"/>
       <c r="C458" s="3"/>
@@ -5131,7 +5131,7 @@
       <c r="E458" s="4"/>
       <c r="F458" s="3"/>
     </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A459" s="4"/>
       <c r="B459" s="3"/>
       <c r="C459" s="3"/>
@@ -5139,7 +5139,7 @@
       <c r="E459" s="4"/>
       <c r="F459" s="3"/>
     </row>
-    <row r="460" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A460" s="4"/>
       <c r="B460" s="3"/>
       <c r="C460" s="3"/>
@@ -5147,7 +5147,7 @@
       <c r="E460" s="4"/>
       <c r="F460" s="3"/>
     </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A461" s="4"/>
       <c r="B461" s="3"/>
       <c r="C461" s="3"/>
@@ -5155,7 +5155,7 @@
       <c r="E461" s="4"/>
       <c r="F461" s="3"/>
     </row>
-    <row r="462" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A462" s="4"/>
       <c r="B462" s="3"/>
       <c r="C462" s="3"/>
@@ -5163,7 +5163,7 @@
       <c r="E462" s="4"/>
       <c r="F462" s="3"/>
     </row>
-    <row r="463" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A463" s="4"/>
       <c r="B463" s="3"/>
       <c r="C463" s="3"/>
@@ -5171,7 +5171,7 @@
       <c r="E463" s="4"/>
       <c r="F463" s="3"/>
     </row>
-    <row r="464" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A464" s="4"/>
       <c r="B464" s="3"/>
       <c r="C464" s="3"/>
@@ -5179,7 +5179,7 @@
       <c r="E464" s="4"/>
       <c r="F464" s="3"/>
     </row>
-    <row r="465" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A465" s="4"/>
       <c r="B465" s="3"/>
       <c r="C465" s="3"/>
@@ -5187,7 +5187,7 @@
       <c r="E465" s="4"/>
       <c r="F465" s="3"/>
     </row>
-    <row r="466" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A466" s="4"/>
       <c r="B466" s="3"/>
       <c r="C466" s="3"/>
@@ -5195,7 +5195,7 @@
       <c r="E466" s="4"/>
       <c r="F466" s="3"/>
     </row>
-    <row r="467" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A467" s="4"/>
       <c r="B467" s="3"/>
       <c r="C467" s="3"/>
@@ -5203,7 +5203,7 @@
       <c r="E467" s="4"/>
       <c r="F467" s="3"/>
     </row>
-    <row r="468" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A468" s="4"/>
       <c r="B468" s="3"/>
       <c r="C468" s="3"/>
@@ -5211,7 +5211,7 @@
       <c r="E468" s="4"/>
       <c r="F468" s="3"/>
     </row>
-    <row r="469" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A469" s="4"/>
       <c r="B469" s="3"/>
       <c r="C469" s="3"/>
@@ -5219,7 +5219,7 @@
       <c r="E469" s="4"/>
       <c r="F469" s="3"/>
     </row>
-    <row r="470" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A470" s="4"/>
       <c r="B470" s="3"/>
       <c r="C470" s="3"/>
@@ -5227,7 +5227,7 @@
       <c r="E470" s="4"/>
       <c r="F470" s="3"/>
     </row>
-    <row r="471" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A471" s="4"/>
       <c r="B471" s="3"/>
       <c r="C471" s="3"/>
@@ -5235,7 +5235,7 @@
       <c r="E471" s="4"/>
       <c r="F471" s="3"/>
     </row>
-    <row r="472" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A472" s="4"/>
       <c r="B472" s="3"/>
       <c r="C472" s="3"/>
@@ -5243,7 +5243,7 @@
       <c r="E472" s="4"/>
       <c r="F472" s="3"/>
     </row>
-    <row r="473" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A473" s="4"/>
       <c r="B473" s="3"/>
       <c r="C473" s="3"/>
@@ -5251,7 +5251,7 @@
       <c r="E473" s="4"/>
       <c r="F473" s="3"/>
     </row>
-    <row r="474" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A474" s="4"/>
       <c r="B474" s="3"/>
       <c r="C474" s="3"/>
@@ -5259,7 +5259,7 @@
       <c r="E474" s="4"/>
       <c r="F474" s="3"/>
     </row>
-    <row r="475" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A475" s="4"/>
       <c r="B475" s="3"/>
       <c r="C475" s="3"/>
@@ -5267,7 +5267,7 @@
       <c r="E475" s="4"/>
       <c r="F475" s="3"/>
     </row>
-    <row r="476" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A476" s="4"/>
       <c r="B476" s="3"/>
       <c r="C476" s="3"/>
@@ -5275,7 +5275,7 @@
       <c r="E476" s="4"/>
       <c r="F476" s="3"/>
     </row>
-    <row r="477" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A477" s="4"/>
       <c r="B477" s="3"/>
       <c r="C477" s="3"/>
@@ -5283,7 +5283,7 @@
       <c r="E477" s="4"/>
       <c r="F477" s="3"/>
     </row>
-    <row r="478" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A478" s="4"/>
       <c r="B478" s="3"/>
       <c r="C478" s="3"/>
@@ -5291,7 +5291,7 @@
       <c r="E478" s="4"/>
       <c r="F478" s="3"/>
     </row>
-    <row r="479" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A479" s="4"/>
       <c r="B479" s="3"/>
       <c r="C479" s="3"/>
@@ -5299,7 +5299,7 @@
       <c r="E479" s="4"/>
       <c r="F479" s="3"/>
     </row>
-    <row r="480" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A480" s="4"/>
       <c r="B480" s="3"/>
       <c r="C480" s="3"/>
@@ -5307,7 +5307,7 @@
       <c r="E480" s="4"/>
       <c r="F480" s="3"/>
     </row>
-    <row r="481" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A481" s="4"/>
       <c r="B481" s="3"/>
       <c r="C481" s="3"/>
@@ -5315,7 +5315,7 @@
       <c r="E481" s="4"/>
       <c r="F481" s="3"/>
     </row>
-    <row r="482" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A482" s="4"/>
       <c r="B482" s="3"/>
       <c r="C482" s="3"/>
@@ -5323,7 +5323,7 @@
       <c r="E482" s="4"/>
       <c r="F482" s="3"/>
     </row>
-    <row r="483" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A483" s="4"/>
       <c r="B483" s="3"/>
       <c r="C483" s="3"/>
@@ -5331,7 +5331,7 @@
       <c r="E483" s="4"/>
       <c r="F483" s="3"/>
     </row>
-    <row r="484" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A484" s="4"/>
       <c r="B484" s="3"/>
       <c r="C484" s="3"/>
@@ -5339,7 +5339,7 @@
       <c r="E484" s="4"/>
       <c r="F484" s="3"/>
     </row>
-    <row r="485" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A485" s="4"/>
       <c r="B485" s="3"/>
       <c r="C485" s="3"/>
@@ -5347,7 +5347,7 @@
       <c r="E485" s="4"/>
       <c r="F485" s="3"/>
     </row>
-    <row r="486" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A486" s="4"/>
       <c r="B486" s="3"/>
       <c r="C486" s="3"/>
@@ -5355,7 +5355,7 @@
       <c r="E486" s="4"/>
       <c r="F486" s="3"/>
     </row>
-    <row r="487" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A487" s="4"/>
       <c r="B487" s="3"/>
       <c r="C487" s="3"/>
@@ -5363,7 +5363,7 @@
       <c r="E487" s="4"/>
       <c r="F487" s="3"/>
     </row>
-    <row r="488" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A488" s="4"/>
       <c r="B488" s="3"/>
       <c r="C488" s="3"/>
@@ -5371,7 +5371,7 @@
       <c r="E488" s="4"/>
       <c r="F488" s="3"/>
     </row>
-    <row r="489" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A489" s="4"/>
       <c r="B489" s="3"/>
       <c r="C489" s="3"/>
@@ -5379,7 +5379,7 @@
       <c r="E489" s="4"/>
       <c r="F489" s="3"/>
     </row>
-    <row r="490" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A490" s="4"/>
       <c r="B490" s="3"/>
       <c r="C490" s="3"/>
@@ -5387,7 +5387,7 @@
       <c r="E490" s="4"/>
       <c r="F490" s="3"/>
     </row>
-    <row r="491" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A491" s="4"/>
       <c r="B491" s="3"/>
       <c r="C491" s="3"/>
@@ -5395,7 +5395,7 @@
       <c r="E491" s="4"/>
       <c r="F491" s="3"/>
     </row>
-    <row r="492" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A492" s="4"/>
       <c r="B492" s="3"/>
       <c r="C492" s="3"/>
@@ -5403,7 +5403,7 @@
       <c r="E492" s="4"/>
       <c r="F492" s="3"/>
     </row>
-    <row r="493" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A493" s="4"/>
       <c r="B493" s="3"/>
       <c r="C493" s="3"/>
@@ -5411,7 +5411,7 @@
       <c r="E493" s="4"/>
       <c r="F493" s="3"/>
     </row>
-    <row r="494" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A494" s="4"/>
       <c r="B494" s="3"/>
       <c r="C494" s="3"/>
@@ -5419,7 +5419,7 @@
       <c r="E494" s="4"/>
       <c r="F494" s="3"/>
     </row>
-    <row r="495" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A495" s="4"/>
       <c r="B495" s="3"/>
       <c r="C495" s="3"/>
@@ -5427,7 +5427,7 @@
       <c r="E495" s="4"/>
       <c r="F495" s="3"/>
     </row>
-    <row r="496" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A496" s="4"/>
       <c r="B496" s="3"/>
       <c r="C496" s="3"/>
@@ -5435,7 +5435,7 @@
       <c r="E496" s="4"/>
       <c r="F496" s="3"/>
     </row>
-    <row r="497" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A497" s="4"/>
       <c r="B497" s="3"/>
       <c r="C497" s="3"/>
@@ -5443,7 +5443,7 @@
       <c r="E497" s="4"/>
       <c r="F497" s="3"/>
     </row>
-    <row r="498" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A498" s="4"/>
       <c r="B498" s="3"/>
       <c r="C498" s="3"/>
@@ -5451,7 +5451,7 @@
       <c r="E498" s="4"/>
       <c r="F498" s="3"/>
     </row>
-    <row r="499" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A499" s="4"/>
       <c r="B499" s="3"/>
       <c r="C499" s="3"/>
@@ -5459,7 +5459,7 @@
       <c r="E499" s="4"/>
       <c r="F499" s="3"/>
     </row>
-    <row r="500" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A500" s="4"/>
       <c r="B500" s="3"/>
       <c r="C500" s="3"/>
@@ -5467,7 +5467,7 @@
       <c r="E500" s="4"/>
       <c r="F500" s="3"/>
     </row>
-    <row r="501" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A501" s="4"/>
       <c r="B501" s="3"/>
       <c r="C501" s="3"/>
@@ -5475,7 +5475,7 @@
       <c r="E501" s="4"/>
       <c r="F501" s="3"/>
     </row>
-    <row r="502" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A502" s="4"/>
       <c r="B502" s="3"/>
       <c r="C502" s="3"/>
@@ -5483,7 +5483,7 @@
       <c r="E502" s="4"/>
       <c r="F502" s="3"/>
     </row>
-    <row r="503" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A503" s="4"/>
       <c r="B503" s="3"/>
       <c r="C503" s="3"/>
@@ -5491,7 +5491,7 @@
       <c r="E503" s="4"/>
       <c r="F503" s="3"/>
     </row>
-    <row r="504" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A504" s="4"/>
       <c r="B504" s="3"/>
       <c r="C504" s="3"/>
@@ -5499,7 +5499,7 @@
       <c r="E504" s="4"/>
       <c r="F504" s="3"/>
     </row>
-    <row r="505" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A505" s="4"/>
       <c r="B505" s="3"/>
       <c r="C505" s="3"/>
@@ -5507,7 +5507,7 @@
       <c r="E505" s="4"/>
       <c r="F505" s="3"/>
     </row>
-    <row r="506" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A506" s="4"/>
       <c r="B506" s="3"/>
       <c r="C506" s="3"/>
@@ -5515,7 +5515,7 @@
       <c r="E506" s="4"/>
       <c r="F506" s="3"/>
     </row>
-    <row r="507" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A507" s="4"/>
       <c r="B507" s="3"/>
       <c r="C507" s="3"/>
@@ -5523,7 +5523,7 @@
       <c r="E507" s="4"/>
       <c r="F507" s="3"/>
     </row>
-    <row r="508" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A508" s="4"/>
       <c r="B508" s="3"/>
       <c r="C508" s="3"/>
@@ -5531,7 +5531,7 @@
       <c r="E508" s="4"/>
       <c r="F508" s="3"/>
     </row>
-    <row r="509" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A509" s="4"/>
       <c r="B509" s="3"/>
       <c r="C509" s="3"/>
@@ -5539,7 +5539,7 @@
       <c r="E509" s="4"/>
       <c r="F509" s="3"/>
     </row>
-    <row r="510" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A510" s="4"/>
       <c r="B510" s="3"/>
       <c r="C510" s="3"/>
@@ -5547,7 +5547,7 @@
       <c r="E510" s="4"/>
       <c r="F510" s="3"/>
     </row>
-    <row r="511" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A511" s="4"/>
       <c r="B511" s="3"/>
       <c r="C511" s="3"/>
@@ -5555,7 +5555,7 @@
       <c r="E511" s="4"/>
       <c r="F511" s="3"/>
     </row>
-    <row r="512" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A512" s="4"/>
       <c r="B512" s="3"/>
       <c r="C512" s="3"/>
@@ -5563,7 +5563,7 @@
       <c r="E512" s="4"/>
       <c r="F512" s="3"/>
     </row>
-    <row r="513" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A513" s="4"/>
       <c r="B513" s="3"/>
       <c r="C513" s="3"/>
@@ -5571,7 +5571,7 @@
       <c r="E513" s="4"/>
       <c r="F513" s="3"/>
     </row>
-    <row r="514" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A514" s="4"/>
       <c r="B514" s="3"/>
       <c r="C514" s="3"/>
@@ -5579,7 +5579,7 @@
       <c r="E514" s="4"/>
       <c r="F514" s="3"/>
     </row>
-    <row r="515" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A515" s="4"/>
       <c r="B515" s="3"/>
       <c r="C515" s="3"/>
@@ -5587,7 +5587,7 @@
       <c r="E515" s="4"/>
       <c r="F515" s="3"/>
     </row>
-    <row r="516" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A516" s="4"/>
       <c r="B516" s="3"/>
       <c r="C516" s="3"/>
@@ -5595,7 +5595,7 @@
       <c r="E516" s="4"/>
       <c r="F516" s="3"/>
     </row>
-    <row r="517" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A517" s="4"/>
       <c r="B517" s="3"/>
       <c r="C517" s="3"/>
@@ -5603,7 +5603,7 @@
       <c r="E517" s="4"/>
       <c r="F517" s="3"/>
     </row>
-    <row r="518" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A518" s="4"/>
       <c r="B518" s="3"/>
       <c r="C518" s="3"/>
@@ -5611,7 +5611,7 @@
       <c r="E518" s="4"/>
       <c r="F518" s="3"/>
     </row>
-    <row r="519" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A519" s="4"/>
       <c r="B519" s="3"/>
       <c r="C519" s="3"/>
@@ -5619,7 +5619,7 @@
       <c r="E519" s="4"/>
       <c r="F519" s="3"/>
     </row>
-    <row r="520" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A520" s="4"/>
       <c r="B520" s="3"/>
       <c r="C520" s="3"/>
@@ -5627,7 +5627,7 @@
       <c r="E520" s="4"/>
       <c r="F520" s="3"/>
     </row>
-    <row r="521" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A521" s="4"/>
       <c r="B521" s="3"/>
       <c r="C521" s="3"/>
@@ -5635,7 +5635,7 @@
       <c r="E521" s="4"/>
       <c r="F521" s="3"/>
     </row>
-    <row r="522" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A522" s="4"/>
       <c r="B522" s="3"/>
       <c r="C522" s="3"/>
@@ -5643,7 +5643,7 @@
       <c r="E522" s="4"/>
       <c r="F522" s="3"/>
     </row>
-    <row r="523" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A523" s="4"/>
       <c r="B523" s="3"/>
       <c r="C523" s="3"/>
@@ -5651,7 +5651,7 @@
       <c r="E523" s="4"/>
       <c r="F523" s="3"/>
     </row>
-    <row r="524" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A524" s="4"/>
       <c r="B524" s="3"/>
       <c r="C524" s="3"/>
@@ -5659,7 +5659,7 @@
       <c r="E524" s="4"/>
       <c r="F524" s="3"/>
     </row>
-    <row r="525" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A525" s="4"/>
       <c r="B525" s="3"/>
       <c r="C525" s="3"/>
@@ -5667,7 +5667,7 @@
       <c r="E525" s="4"/>
       <c r="F525" s="3"/>
     </row>
-    <row r="526" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A526" s="4"/>
       <c r="B526" s="3"/>
       <c r="C526" s="3"/>
@@ -5675,7 +5675,7 @@
       <c r="E526" s="4"/>
       <c r="F526" s="3"/>
     </row>
-    <row r="527" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A527" s="4"/>
       <c r="B527" s="3"/>
       <c r="C527" s="3"/>
@@ -5683,7 +5683,7 @@
       <c r="E527" s="4"/>
       <c r="F527" s="3"/>
     </row>
-    <row r="528" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A528" s="4"/>
       <c r="B528" s="3"/>
       <c r="C528" s="3"/>
@@ -5691,7 +5691,7 @@
       <c r="E528" s="4"/>
       <c r="F528" s="3"/>
     </row>
-    <row r="529" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A529" s="4"/>
       <c r="B529" s="3"/>
       <c r="C529" s="3"/>
@@ -5699,7 +5699,7 @@
       <c r="E529" s="4"/>
       <c r="F529" s="3"/>
     </row>
-    <row r="530" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A530" s="4"/>
       <c r="B530" s="3"/>
       <c r="C530" s="3"/>
@@ -5707,7 +5707,7 @@
       <c r="E530" s="4"/>
       <c r="F530" s="3"/>
     </row>
-    <row r="531" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A531" s="4"/>
       <c r="B531" s="3"/>
       <c r="C531" s="3"/>
@@ -5715,7 +5715,7 @@
       <c r="E531" s="4"/>
       <c r="F531" s="3"/>
     </row>
-    <row r="532" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A532" s="4"/>
       <c r="B532" s="3"/>
       <c r="C532" s="3"/>
@@ -5723,7 +5723,7 @@
       <c r="E532" s="4"/>
       <c r="F532" s="3"/>
     </row>
-    <row r="533" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A533" s="4"/>
       <c r="B533" s="3"/>
       <c r="C533" s="3"/>
@@ -5731,7 +5731,7 @@
       <c r="E533" s="4"/>
       <c r="F533" s="3"/>
     </row>
-    <row r="534" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A534" s="4"/>
       <c r="B534" s="3"/>
       <c r="C534" s="3"/>
@@ -5739,7 +5739,7 @@
       <c r="E534" s="4"/>
       <c r="F534" s="3"/>
     </row>
-    <row r="535" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A535" s="4"/>
       <c r="B535" s="3"/>
       <c r="C535" s="3"/>
@@ -5747,7 +5747,7 @@
       <c r="E535" s="4"/>
       <c r="F535" s="3"/>
     </row>
-    <row r="536" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A536" s="4"/>
       <c r="B536" s="3"/>
       <c r="C536" s="3"/>
@@ -5755,7 +5755,7 @@
       <c r="E536" s="4"/>
       <c r="F536" s="3"/>
     </row>
-    <row r="537" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A537" s="4"/>
       <c r="B537" s="3"/>
       <c r="C537" s="3"/>
@@ -5763,7 +5763,7 @@
       <c r="E537" s="4"/>
       <c r="F537" s="3"/>
     </row>
-    <row r="538" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A538" s="4"/>
       <c r="B538" s="3"/>
       <c r="C538" s="3"/>
@@ -5771,7 +5771,7 @@
       <c r="E538" s="4"/>
       <c r="F538" s="3"/>
     </row>
-    <row r="539" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A539" s="4"/>
       <c r="B539" s="3"/>
       <c r="C539" s="3"/>
@@ -5779,7 +5779,7 @@
       <c r="E539" s="4"/>
       <c r="F539" s="3"/>
     </row>
-    <row r="540" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A540" s="4"/>
       <c r="B540" s="3"/>
       <c r="C540" s="3"/>
@@ -5787,7 +5787,7 @@
       <c r="E540" s="4"/>
       <c r="F540" s="3"/>
     </row>
-    <row r="541" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A541" s="4"/>
       <c r="B541" s="3"/>
       <c r="C541" s="3"/>
@@ -5795,7 +5795,7 @@
       <c r="E541" s="4"/>
       <c r="F541" s="3"/>
     </row>
-    <row r="542" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A542" s="4"/>
       <c r="B542" s="3"/>
       <c r="C542" s="3"/>
@@ -5803,7 +5803,7 @@
       <c r="E542" s="4"/>
       <c r="F542" s="3"/>
     </row>
-    <row r="543" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A543" s="4"/>
       <c r="B543" s="3"/>
       <c r="C543" s="3"/>
@@ -5811,7 +5811,7 @@
       <c r="E543" s="4"/>
       <c r="F543" s="3"/>
     </row>
-    <row r="544" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A544" s="4"/>
       <c r="B544" s="3"/>
       <c r="C544" s="3"/>
@@ -5819,7 +5819,7 @@
       <c r="E544" s="4"/>
       <c r="F544" s="3"/>
     </row>
-    <row r="545" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A545" s="4"/>
       <c r="B545" s="3"/>
       <c r="C545" s="3"/>
@@ -5827,7 +5827,7 @@
       <c r="E545" s="4"/>
       <c r="F545" s="3"/>
     </row>
-    <row r="546" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A546" s="4"/>
       <c r="B546" s="3"/>
       <c r="C546" s="3"/>
@@ -5835,7 +5835,7 @@
       <c r="E546" s="4"/>
       <c r="F546" s="3"/>
     </row>
-    <row r="547" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A547" s="4"/>
       <c r="B547" s="3"/>
       <c r="C547" s="3"/>
@@ -5843,7 +5843,7 @@
       <c r="E547" s="4"/>
       <c r="F547" s="3"/>
     </row>
-    <row r="548" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A548" s="4"/>
       <c r="B548" s="3"/>
       <c r="C548" s="3"/>
@@ -5851,7 +5851,7 @@
       <c r="E548" s="4"/>
       <c r="F548" s="3"/>
     </row>
-    <row r="549" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A549" s="4"/>
       <c r="B549" s="3"/>
       <c r="C549" s="3"/>
@@ -5859,7 +5859,7 @@
       <c r="E549" s="4"/>
       <c r="F549" s="3"/>
     </row>
-    <row r="550" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A550" s="4"/>
       <c r="B550" s="3"/>
       <c r="C550" s="3"/>
@@ -5867,7 +5867,7 @@
       <c r="E550" s="4"/>
       <c r="F550" s="3"/>
     </row>
-    <row r="551" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A551" s="4"/>
       <c r="B551" s="3"/>
       <c r="C551" s="3"/>
@@ -5875,7 +5875,7 @@
       <c r="E551" s="4"/>
       <c r="F551" s="3"/>
     </row>
-    <row r="552" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A552" s="4"/>
       <c r="B552" s="3"/>
       <c r="C552" s="3"/>
@@ -5883,7 +5883,7 @@
       <c r="E552" s="4"/>
       <c r="F552" s="3"/>
     </row>
-    <row r="553" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A553" s="4"/>
       <c r="B553" s="3"/>
       <c r="C553" s="3"/>
@@ -5891,7 +5891,7 @@
       <c r="E553" s="4"/>
       <c r="F553" s="3"/>
     </row>
-    <row r="554" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A554" s="4"/>
       <c r="B554" s="3"/>
       <c r="C554" s="3"/>
@@ -5899,7 +5899,7 @@
       <c r="E554" s="4"/>
       <c r="F554" s="3"/>
     </row>
-    <row r="555" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A555" s="4"/>
       <c r="B555" s="3"/>
       <c r="C555" s="3"/>
@@ -5907,7 +5907,7 @@
       <c r="E555" s="4"/>
       <c r="F555" s="3"/>
     </row>
-    <row r="556" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A556" s="4"/>
       <c r="B556" s="3"/>
       <c r="C556" s="3"/>
@@ -5915,7 +5915,7 @@
       <c r="E556" s="4"/>
       <c r="F556" s="3"/>
     </row>
-    <row r="557" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A557" s="4"/>
       <c r="B557" s="3"/>
       <c r="C557" s="3"/>
@@ -5923,7 +5923,7 @@
       <c r="E557" s="4"/>
       <c r="F557" s="3"/>
     </row>
-    <row r="558" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A558" s="4"/>
       <c r="B558" s="3"/>
       <c r="C558" s="3"/>
@@ -5931,7 +5931,7 @@
       <c r="E558" s="4"/>
       <c r="F558" s="3"/>
     </row>
-    <row r="559" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A559" s="4"/>
       <c r="B559" s="3"/>
       <c r="C559" s="3"/>
@@ -5939,7 +5939,7 @@
       <c r="E559" s="4"/>
       <c r="F559" s="3"/>
     </row>
-    <row r="560" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A560" s="4"/>
       <c r="B560" s="3"/>
       <c r="C560" s="3"/>
@@ -5947,7 +5947,7 @@
       <c r="E560" s="4"/>
       <c r="F560" s="3"/>
     </row>
-    <row r="561" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A561" s="4"/>
       <c r="B561" s="3"/>
       <c r="C561" s="3"/>
@@ -5955,7 +5955,7 @@
       <c r="E561" s="4"/>
       <c r="F561" s="3"/>
     </row>
-    <row r="562" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A562" s="4"/>
       <c r="B562" s="3"/>
       <c r="C562" s="3"/>
@@ -5963,7 +5963,7 @@
       <c r="E562" s="4"/>
       <c r="F562" s="3"/>
     </row>
-    <row r="563" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A563" s="4"/>
       <c r="B563" s="3"/>
       <c r="C563" s="3"/>
@@ -5971,7 +5971,7 @@
       <c r="E563" s="4"/>
       <c r="F563" s="3"/>
     </row>
-    <row r="564" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A564" s="4"/>
       <c r="B564" s="3"/>
       <c r="C564" s="3"/>
@@ -5979,7 +5979,7 @@
       <c r="E564" s="4"/>
       <c r="F564" s="3"/>
     </row>
-    <row r="565" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A565" s="4"/>
       <c r="B565" s="3"/>
       <c r="C565" s="3"/>
@@ -5987,7 +5987,7 @@
       <c r="E565" s="4"/>
       <c r="F565" s="3"/>
     </row>
-    <row r="566" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A566" s="4"/>
       <c r="B566" s="3"/>
       <c r="C566" s="3"/>
@@ -5995,7 +5995,7 @@
       <c r="E566" s="4"/>
       <c r="F566" s="3"/>
     </row>
-    <row r="567" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A567" s="4"/>
       <c r="B567" s="3"/>
       <c r="C567" s="3"/>
@@ -6003,7 +6003,7 @@
       <c r="E567" s="4"/>
       <c r="F567" s="3"/>
     </row>
-    <row r="568" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A568" s="4"/>
       <c r="B568" s="3"/>
       <c r="C568" s="3"/>
@@ -6011,7 +6011,7 @@
       <c r="E568" s="4"/>
       <c r="F568" s="3"/>
     </row>
-    <row r="569" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A569" s="4"/>
       <c r="B569" s="3"/>
       <c r="C569" s="3"/>
@@ -6019,7 +6019,7 @@
       <c r="E569" s="4"/>
       <c r="F569" s="3"/>
     </row>
-    <row r="570" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A570" s="4"/>
       <c r="B570" s="3"/>
       <c r="C570" s="3"/>
@@ -6027,7 +6027,7 @@
       <c r="E570" s="4"/>
       <c r="F570" s="3"/>
     </row>
-    <row r="571" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A571" s="4"/>
       <c r="B571" s="3"/>
       <c r="C571" s="3"/>
@@ -6035,7 +6035,7 @@
       <c r="E571" s="4"/>
       <c r="F571" s="3"/>
     </row>
-    <row r="572" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A572" s="4"/>
       <c r="B572" s="3"/>
       <c r="C572" s="3"/>
@@ -6043,7 +6043,7 @@
       <c r="E572" s="4"/>
       <c r="F572" s="3"/>
     </row>
-    <row r="573" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A573" s="4"/>
       <c r="B573" s="3"/>
       <c r="C573" s="3"/>
@@ -6051,7 +6051,7 @@
       <c r="E573" s="4"/>
       <c r="F573" s="3"/>
     </row>
-    <row r="574" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A574" s="4"/>
       <c r="B574" s="3"/>
       <c r="C574" s="3"/>
@@ -6059,7 +6059,7 @@
       <c r="E574" s="4"/>
       <c r="F574" s="3"/>
     </row>
-    <row r="575" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A575" s="4"/>
       <c r="B575" s="3"/>
       <c r="C575" s="3"/>
@@ -6067,7 +6067,7 @@
       <c r="E575" s="4"/>
       <c r="F575" s="3"/>
     </row>
-    <row r="576" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A576" s="4"/>
       <c r="B576" s="3"/>
       <c r="C576" s="3"/>
@@ -6075,7 +6075,7 @@
       <c r="E576" s="4"/>
       <c r="F576" s="3"/>
     </row>
-    <row r="577" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A577" s="4"/>
       <c r="B577" s="3"/>
       <c r="C577" s="3"/>
@@ -6083,7 +6083,7 @@
       <c r="E577" s="4"/>
       <c r="F577" s="3"/>
     </row>
-    <row r="578" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A578" s="4"/>
       <c r="B578" s="3"/>
       <c r="C578" s="3"/>
@@ -6091,7 +6091,7 @@
       <c r="E578" s="4"/>
       <c r="F578" s="3"/>
     </row>
-    <row r="579" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A579" s="4"/>
       <c r="B579" s="3"/>
       <c r="C579" s="3"/>
@@ -6099,7 +6099,7 @@
       <c r="E579" s="4"/>
       <c r="F579" s="3"/>
     </row>
-    <row r="580" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A580" s="4"/>
       <c r="B580" s="3"/>
       <c r="C580" s="3"/>
@@ -6107,7 +6107,7 @@
       <c r="E580" s="4"/>
       <c r="F580" s="3"/>
     </row>
-    <row r="581" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A581" s="4"/>
       <c r="B581" s="3"/>
       <c r="C581" s="3"/>
@@ -6115,7 +6115,7 @@
       <c r="E581" s="4"/>
       <c r="F581" s="3"/>
     </row>
-    <row r="582" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A582" s="4"/>
       <c r="B582" s="3"/>
       <c r="C582" s="3"/>
@@ -6123,7 +6123,7 @@
       <c r="E582" s="4"/>
       <c r="F582" s="3"/>
     </row>
-    <row r="583" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A583" s="4"/>
       <c r="B583" s="3"/>
       <c r="C583" s="3"/>
@@ -6131,7 +6131,7 @@
       <c r="E583" s="4"/>
       <c r="F583" s="3"/>
     </row>
-    <row r="584" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A584" s="4"/>
       <c r="B584" s="3"/>
       <c r="C584" s="3"/>
@@ -6139,7 +6139,7 @@
       <c r="E584" s="4"/>
       <c r="F584" s="3"/>
     </row>
-    <row r="585" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A585" s="4"/>
       <c r="B585" s="3"/>
       <c r="C585" s="3"/>
@@ -6147,7 +6147,7 @@
       <c r="E585" s="4"/>
       <c r="F585" s="3"/>
     </row>
-    <row r="586" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A586" s="4"/>
       <c r="B586" s="3"/>
       <c r="C586" s="3"/>
@@ -6155,7 +6155,7 @@
       <c r="E586" s="4"/>
       <c r="F586" s="3"/>
     </row>
-    <row r="587" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A587" s="4"/>
       <c r="B587" s="3"/>
       <c r="C587" s="3"/>
@@ -6163,7 +6163,7 @@
       <c r="E587" s="4"/>
       <c r="F587" s="3"/>
     </row>
-    <row r="588" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A588" s="4"/>
       <c r="B588" s="3"/>
       <c r="C588" s="3"/>
@@ -6171,7 +6171,7 @@
       <c r="E588" s="4"/>
       <c r="F588" s="3"/>
     </row>
-    <row r="589" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A589" s="4"/>
       <c r="B589" s="3"/>
       <c r="C589" s="3"/>
@@ -6179,7 +6179,7 @@
       <c r="E589" s="4"/>
       <c r="F589" s="3"/>
     </row>
-    <row r="590" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A590" s="4"/>
       <c r="B590" s="3"/>
       <c r="C590" s="3"/>
@@ -6187,7 +6187,7 @@
       <c r="E590" s="4"/>
       <c r="F590" s="3"/>
     </row>
-    <row r="591" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A591" s="4"/>
       <c r="B591" s="3"/>
       <c r="C591" s="3"/>
@@ -6195,7 +6195,7 @@
       <c r="E591" s="4"/>
       <c r="F591" s="3"/>
     </row>
-    <row r="592" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A592" s="4"/>
       <c r="B592" s="3"/>
       <c r="C592" s="3"/>
@@ -6203,7 +6203,7 @@
       <c r="E592" s="4"/>
       <c r="F592" s="3"/>
     </row>
-    <row r="593" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A593" s="4"/>
       <c r="B593" s="3"/>
       <c r="C593" s="3"/>
@@ -6211,7 +6211,7 @@
       <c r="E593" s="4"/>
       <c r="F593" s="3"/>
     </row>
-    <row r="594" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A594" s="4"/>
       <c r="B594" s="3"/>
       <c r="C594" s="3"/>
@@ -6219,7 +6219,7 @@
       <c r="E594" s="4"/>
       <c r="F594" s="3"/>
     </row>
-    <row r="595" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A595" s="4"/>
       <c r="B595" s="3"/>
       <c r="C595" s="3"/>
@@ -6227,7 +6227,7 @@
       <c r="E595" s="4"/>
       <c r="F595" s="3"/>
     </row>
-    <row r="596" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A596" s="4"/>
       <c r="B596" s="3"/>
       <c r="C596" s="3"/>
@@ -6235,7 +6235,7 @@
       <c r="E596" s="4"/>
       <c r="F596" s="3"/>
     </row>
-    <row r="597" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A597" s="4"/>
       <c r="B597" s="3"/>
       <c r="C597" s="3"/>
@@ -6243,7 +6243,7 @@
       <c r="E597" s="4"/>
       <c r="F597" s="3"/>
     </row>
-    <row r="598" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A598" s="4"/>
       <c r="B598" s="3"/>
       <c r="C598" s="3"/>
@@ -6251,7 +6251,7 @@
       <c r="E598" s="4"/>
       <c r="F598" s="3"/>
     </row>
-    <row r="599" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A599" s="4"/>
       <c r="B599" s="3"/>
       <c r="C599" s="3"/>
@@ -6259,7 +6259,7 @@
       <c r="E599" s="4"/>
       <c r="F599" s="3"/>
     </row>
-    <row r="600" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A600" s="4"/>
       <c r="B600" s="3"/>
       <c r="C600" s="3"/>
@@ -6267,7 +6267,7 @@
       <c r="E600" s="4"/>
       <c r="F600" s="3"/>
     </row>
-    <row r="601" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A601" s="4"/>
       <c r="B601" s="3"/>
       <c r="C601" s="3"/>
@@ -6275,7 +6275,7 @@
       <c r="E601" s="4"/>
       <c r="F601" s="3"/>
     </row>
-    <row r="602" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A602" s="4"/>
       <c r="B602" s="3"/>
       <c r="C602" s="3"/>
@@ -6283,7 +6283,7 @@
       <c r="E602" s="4"/>
       <c r="F602" s="3"/>
     </row>
-    <row r="603" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A603" s="4"/>
       <c r="B603" s="3"/>
       <c r="C603" s="3"/>
@@ -6291,7 +6291,7 @@
       <c r="E603" s="4"/>
       <c r="F603" s="3"/>
     </row>
-    <row r="604" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A604" s="4"/>
       <c r="B604" s="3"/>
       <c r="C604" s="3"/>
@@ -6299,7 +6299,7 @@
       <c r="E604" s="4"/>
       <c r="F604" s="3"/>
     </row>
-    <row r="605" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A605" s="4"/>
       <c r="B605" s="3"/>
       <c r="C605" s="3"/>
@@ -6307,7 +6307,7 @@
       <c r="E605" s="4"/>
       <c r="F605" s="3"/>
     </row>
-    <row r="606" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A606" s="4"/>
       <c r="B606" s="3"/>
       <c r="C606" s="3"/>
@@ -6315,7 +6315,7 @@
       <c r="E606" s="4"/>
       <c r="F606" s="3"/>
     </row>
-    <row r="607" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A607" s="4"/>
       <c r="B607" s="3"/>
       <c r="C607" s="3"/>
@@ -6323,7 +6323,7 @@
       <c r="E607" s="4"/>
       <c r="F607" s="3"/>
     </row>
-    <row r="608" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A608" s="4"/>
       <c r="B608" s="3"/>
       <c r="C608" s="3"/>
@@ -6331,7 +6331,7 @@
       <c r="E608" s="4"/>
       <c r="F608" s="3"/>
     </row>
-    <row r="609" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A609" s="4"/>
       <c r="B609" s="3"/>
       <c r="C609" s="3"/>
@@ -6339,7 +6339,7 @@
       <c r="E609" s="4"/>
       <c r="F609" s="3"/>
     </row>
-    <row r="610" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A610" s="4"/>
       <c r="B610" s="3"/>
       <c r="C610" s="3"/>
@@ -6347,7 +6347,7 @@
       <c r="E610" s="4"/>
       <c r="F610" s="3"/>
     </row>
-    <row r="611" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A611" s="4"/>
       <c r="B611" s="3"/>
       <c r="C611" s="3"/>
@@ -6355,7 +6355,7 @@
       <c r="E611" s="4"/>
       <c r="F611" s="3"/>
     </row>
-    <row r="612" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A612" s="4"/>
       <c r="B612" s="3"/>
       <c r="C612" s="3"/>
@@ -6363,7 +6363,7 @@
       <c r="E612" s="4"/>
       <c r="F612" s="3"/>
     </row>
-    <row r="613" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A613" s="4"/>
       <c r="B613" s="3"/>
       <c r="C613" s="3"/>
@@ -6371,7 +6371,7 @@
       <c r="E613" s="4"/>
       <c r="F613" s="3"/>
     </row>
-    <row r="614" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A614" s="4"/>
       <c r="B614" s="3"/>
       <c r="C614" s="3"/>
@@ -6379,7 +6379,7 @@
       <c r="E614" s="4"/>
       <c r="F614" s="3"/>
     </row>
-    <row r="615" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A615" s="4"/>
       <c r="B615" s="3"/>
       <c r="C615" s="3"/>
@@ -6387,7 +6387,7 @@
       <c r="E615" s="4"/>
       <c r="F615" s="3"/>
     </row>
-    <row r="616" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A616" s="4"/>
       <c r="B616" s="3"/>
       <c r="C616" s="3"/>
@@ -6395,7 +6395,7 @@
       <c r="E616" s="4"/>
       <c r="F616" s="3"/>
     </row>
-    <row r="617" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A617" s="4"/>
       <c r="B617" s="3"/>
       <c r="C617" s="3"/>
@@ -6403,7 +6403,7 @@
       <c r="E617" s="4"/>
       <c r="F617" s="3"/>
     </row>
-    <row r="618" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A618" s="4"/>
       <c r="B618" s="3"/>
       <c r="C618" s="3"/>
@@ -6411,7 +6411,7 @@
       <c r="E618" s="4"/>
       <c r="F618" s="3"/>
     </row>
-    <row r="619" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A619" s="4"/>
       <c r="B619" s="3"/>
       <c r="C619" s="3"/>
@@ -6419,7 +6419,7 @@
       <c r="E619" s="4"/>
       <c r="F619" s="3"/>
     </row>
-    <row r="620" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A620" s="4"/>
       <c r="B620" s="3"/>
       <c r="C620" s="3"/>
@@ -6427,7 +6427,7 @@
       <c r="E620" s="4"/>
       <c r="F620" s="3"/>
     </row>
-    <row r="621" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A621" s="4"/>
       <c r="B621" s="3"/>
       <c r="C621" s="3"/>
@@ -6435,7 +6435,7 @@
       <c r="E621" s="4"/>
       <c r="F621" s="3"/>
     </row>
-    <row r="622" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A622" s="4"/>
       <c r="B622" s="3"/>
       <c r="C622" s="3"/>
@@ -6443,7 +6443,7 @@
       <c r="E622" s="4"/>
       <c r="F622" s="3"/>
     </row>
-    <row r="623" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A623" s="4"/>
       <c r="B623" s="3"/>
       <c r="C623" s="3"/>
@@ -6451,7 +6451,7 @@
       <c r="E623" s="4"/>
       <c r="F623" s="3"/>
     </row>
-    <row r="624" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A624" s="4"/>
       <c r="B624" s="3"/>
       <c r="C624" s="3"/>
@@ -6459,7 +6459,7 @@
       <c r="E624" s="4"/>
       <c r="F624" s="3"/>
     </row>
-    <row r="625" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A625" s="4"/>
       <c r="B625" s="3"/>
       <c r="C625" s="3"/>
@@ -6467,7 +6467,7 @@
       <c r="E625" s="4"/>
       <c r="F625" s="3"/>
     </row>
-    <row r="626" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A626" s="4"/>
       <c r="B626" s="3"/>
       <c r="C626" s="3"/>
@@ -6475,7 +6475,7 @@
       <c r="E626" s="4"/>
       <c r="F626" s="3"/>
     </row>
-    <row r="627" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A627" s="4"/>
       <c r="B627" s="3"/>
       <c r="C627" s="3"/>
@@ -6483,7 +6483,7 @@
       <c r="E627" s="4"/>
       <c r="F627" s="3"/>
     </row>
-    <row r="628" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A628" s="4"/>
       <c r="B628" s="3"/>
       <c r="C628" s="3"/>
@@ -6491,7 +6491,7 @@
       <c r="E628" s="4"/>
       <c r="F628" s="3"/>
     </row>
-    <row r="629" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A629" s="4"/>
       <c r="B629" s="3"/>
       <c r="C629" s="3"/>
@@ -6499,7 +6499,7 @@
       <c r="E629" s="4"/>
       <c r="F629" s="3"/>
     </row>
-    <row r="630" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A630" s="4"/>
       <c r="B630" s="3"/>
       <c r="C630" s="3"/>
@@ -6507,7 +6507,7 @@
       <c r="E630" s="4"/>
       <c r="F630" s="3"/>
     </row>
-    <row r="631" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A631" s="4"/>
       <c r="B631" s="3"/>
       <c r="C631" s="3"/>
@@ -6515,7 +6515,7 @@
       <c r="E631" s="4"/>
       <c r="F631" s="3"/>
     </row>
-    <row r="632" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A632" s="4"/>
       <c r="B632" s="3"/>
       <c r="C632" s="3"/>
@@ -6523,7 +6523,7 @@
       <c r="E632" s="4"/>
       <c r="F632" s="3"/>
     </row>
-    <row r="633" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A633" s="4"/>
       <c r="B633" s="3"/>
       <c r="C633" s="3"/>
@@ -6531,7 +6531,7 @@
       <c r="E633" s="4"/>
       <c r="F633" s="3"/>
     </row>
-    <row r="634" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A634" s="4"/>
       <c r="B634" s="3"/>
       <c r="C634" s="3"/>
@@ -6539,7 +6539,7 @@
       <c r="E634" s="4"/>
       <c r="F634" s="3"/>
     </row>
-    <row r="635" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A635" s="4"/>
       <c r="B635" s="3"/>
       <c r="C635" s="3"/>
@@ -6547,7 +6547,7 @@
       <c r="E635" s="4"/>
       <c r="F635" s="3"/>
     </row>
-    <row r="636" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A636" s="4"/>
       <c r="B636" s="3"/>
       <c r="C636" s="3"/>
@@ -6555,7 +6555,7 @@
       <c r="E636" s="4"/>
       <c r="F636" s="3"/>
     </row>
-    <row r="637" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A637" s="4"/>
       <c r="B637" s="3"/>
       <c r="C637" s="3"/>
@@ -6563,7 +6563,7 @@
       <c r="E637" s="4"/>
       <c r="F637" s="3"/>
     </row>
-    <row r="638" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A638" s="4"/>
       <c r="B638" s="3"/>
       <c r="C638" s="3"/>
@@ -6571,7 +6571,7 @@
       <c r="E638" s="4"/>
       <c r="F638" s="3"/>
     </row>
-    <row r="639" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A639" s="4"/>
       <c r="B639" s="3"/>
       <c r="C639" s="3"/>
@@ -6579,7 +6579,7 @@
       <c r="E639" s="4"/>
       <c r="F639" s="3"/>
     </row>
-    <row r="640" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A640" s="4"/>
       <c r="B640" s="3"/>
       <c r="C640" s="3"/>
@@ -6587,7 +6587,7 @@
       <c r="E640" s="4"/>
       <c r="F640" s="3"/>
     </row>
-    <row r="641" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A641" s="4"/>
       <c r="B641" s="3"/>
       <c r="C641" s="3"/>
@@ -6595,7 +6595,7 @@
       <c r="E641" s="4"/>
       <c r="F641" s="3"/>
     </row>
-    <row r="642" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A642" s="4"/>
       <c r="B642" s="3"/>
       <c r="C642" s="3"/>
@@ -6603,7 +6603,7 @@
       <c r="E642" s="4"/>
       <c r="F642" s="3"/>
     </row>
-    <row r="643" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A643" s="4"/>
       <c r="B643" s="3"/>
       <c r="C643" s="3"/>
@@ -6611,7 +6611,7 @@
       <c r="E643" s="4"/>
       <c r="F643" s="3"/>
     </row>
-    <row r="644" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A644" s="4"/>
       <c r="B644" s="3"/>
       <c r="C644" s="3"/>
@@ -6619,7 +6619,7 @@
       <c r="E644" s="4"/>
       <c r="F644" s="3"/>
     </row>
-    <row r="645" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A645" s="4"/>
       <c r="B645" s="3"/>
       <c r="C645" s="3"/>
@@ -6627,7 +6627,7 @@
       <c r="E645" s="4"/>
       <c r="F645" s="3"/>
     </row>
-    <row r="646" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A646" s="4"/>
       <c r="B646" s="3"/>
       <c r="C646" s="3"/>
@@ -6635,7 +6635,7 @@
       <c r="E646" s="4"/>
       <c r="F646" s="3"/>
     </row>
-    <row r="647" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A647" s="4"/>
       <c r="B647" s="3"/>
       <c r="C647" s="3"/>
@@ -6643,7 +6643,7 @@
       <c r="E647" s="4"/>
       <c r="F647" s="3"/>
     </row>
-    <row r="648" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A648" s="4"/>
       <c r="B648" s="3"/>
       <c r="C648" s="3"/>
@@ -6651,7 +6651,7 @@
       <c r="E648" s="4"/>
       <c r="F648" s="3"/>
     </row>
-    <row r="649" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A649" s="4"/>
       <c r="B649" s="3"/>
       <c r="C649" s="3"/>
@@ -6659,7 +6659,7 @@
       <c r="E649" s="4"/>
       <c r="F649" s="3"/>
     </row>
-    <row r="650" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A650" s="4"/>
       <c r="B650" s="3"/>
       <c r="C650" s="3"/>
@@ -6667,7 +6667,7 @@
       <c r="E650" s="4"/>
       <c r="F650" s="3"/>
     </row>
-    <row r="651" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A651" s="4"/>
       <c r="B651" s="3"/>
       <c r="C651" s="3"/>
@@ -6675,7 +6675,7 @@
       <c r="E651" s="4"/>
       <c r="F651" s="3"/>
     </row>
-    <row r="652" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A652" s="4"/>
       <c r="B652" s="3"/>
       <c r="C652" s="3"/>
@@ -6683,7 +6683,7 @@
       <c r="E652" s="4"/>
       <c r="F652" s="3"/>
     </row>
-    <row r="653" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A653" s="4"/>
       <c r="B653" s="3"/>
       <c r="C653" s="3"/>
@@ -6691,7 +6691,7 @@
       <c r="E653" s="4"/>
       <c r="F653" s="3"/>
     </row>
-    <row r="654" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A654" s="4"/>
       <c r="B654" s="3"/>
       <c r="C654" s="3"/>
@@ -6699,7 +6699,7 @@
       <c r="E654" s="4"/>
       <c r="F654" s="3"/>
     </row>
-    <row r="655" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A655" s="4"/>
       <c r="B655" s="3"/>
       <c r="C655" s="3"/>
@@ -6707,7 +6707,7 @@
       <c r="E655" s="4"/>
       <c r="F655" s="3"/>
     </row>
-    <row r="656" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A656" s="4"/>
       <c r="B656" s="3"/>
       <c r="C656" s="3"/>
@@ -6715,7 +6715,7 @@
       <c r="E656" s="4"/>
       <c r="F656" s="3"/>
     </row>
-    <row r="657" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A657" s="4"/>
       <c r="B657" s="3"/>
       <c r="C657" s="3"/>
@@ -6723,7 +6723,7 @@
       <c r="E657" s="4"/>
       <c r="F657" s="3"/>
     </row>
-    <row r="658" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A658" s="4"/>
       <c r="B658" s="3"/>
       <c r="C658" s="3"/>
@@ -6731,7 +6731,7 @@
       <c r="E658" s="4"/>
       <c r="F658" s="3"/>
     </row>
-    <row r="659" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A659" s="4"/>
       <c r="B659" s="3"/>
       <c r="C659" s="3"/>
@@ -6739,7 +6739,7 @@
       <c r="E659" s="4"/>
       <c r="F659" s="3"/>
     </row>
-    <row r="660" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A660" s="4"/>
       <c r="B660" s="3"/>
       <c r="C660" s="3"/>
@@ -6747,7 +6747,7 @@
       <c r="E660" s="4"/>
       <c r="F660" s="3"/>
     </row>
-    <row r="661" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A661" s="4"/>
       <c r="B661" s="3"/>
       <c r="C661" s="3"/>
@@ -6755,7 +6755,7 @@
       <c r="E661" s="4"/>
       <c r="F661" s="3"/>
     </row>
-    <row r="662" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A662" s="4"/>
       <c r="B662" s="3"/>
       <c r="C662" s="3"/>
@@ -6763,7 +6763,7 @@
       <c r="E662" s="4"/>
       <c r="F662" s="3"/>
     </row>
-    <row r="663" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A663" s="4"/>
       <c r="B663" s="3"/>
       <c r="C663" s="3"/>
@@ -6771,7 +6771,7 @@
       <c r="E663" s="4"/>
       <c r="F663" s="3"/>
     </row>
-    <row r="664" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A664" s="4"/>
       <c r="B664" s="3"/>
       <c r="C664" s="3"/>
@@ -6779,7 +6779,7 @@
       <c r="E664" s="4"/>
       <c r="F664" s="3"/>
     </row>
-    <row r="665" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A665" s="4"/>
       <c r="B665" s="3"/>
       <c r="C665" s="3"/>
@@ -6787,7 +6787,7 @@
       <c r="E665" s="4"/>
       <c r="F665" s="3"/>
     </row>
-    <row r="666" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A666" s="4"/>
       <c r="B666" s="3"/>
       <c r="C666" s="3"/>
@@ -6795,7 +6795,7 @@
       <c r="E666" s="4"/>
       <c r="F666" s="3"/>
     </row>
-    <row r="667" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A667" s="4"/>
       <c r="B667" s="3"/>
       <c r="C667" s="3"/>
@@ -6803,7 +6803,7 @@
       <c r="E667" s="4"/>
       <c r="F667" s="3"/>
     </row>
-    <row r="668" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A668" s="4"/>
       <c r="B668" s="3"/>
       <c r="C668" s="3"/>
@@ -6811,7 +6811,7 @@
       <c r="E668" s="4"/>
       <c r="F668" s="3"/>
     </row>
-    <row r="669" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A669" s="4"/>
       <c r="B669" s="3"/>
       <c r="C669" s="3"/>
@@ -6819,7 +6819,7 @@
       <c r="E669" s="4"/>
       <c r="F669" s="3"/>
     </row>
-    <row r="670" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A670" s="4"/>
       <c r="B670" s="3"/>
       <c r="C670" s="3"/>
@@ -6827,7 +6827,7 @@
       <c r="E670" s="4"/>
       <c r="F670" s="3"/>
     </row>
-    <row r="671" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A671" s="4"/>
       <c r="B671" s="3"/>
       <c r="C671" s="3"/>
@@ -6835,7 +6835,7 @@
       <c r="E671" s="4"/>
       <c r="F671" s="3"/>
     </row>
-    <row r="672" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A672" s="4"/>
       <c r="B672" s="3"/>
       <c r="C672" s="3"/>
@@ -6843,7 +6843,7 @@
       <c r="E672" s="4"/>
       <c r="F672" s="3"/>
     </row>
-    <row r="673" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A673" s="4"/>
       <c r="B673" s="3"/>
       <c r="C673" s="3"/>
@@ -6851,7 +6851,7 @@
       <c r="E673" s="4"/>
       <c r="F673" s="3"/>
     </row>
-    <row r="674" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A674" s="4"/>
       <c r="B674" s="3"/>
       <c r="C674" s="3"/>
@@ -6859,7 +6859,7 @@
       <c r="E674" s="4"/>
       <c r="F674" s="3"/>
     </row>
-    <row r="675" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A675" s="4"/>
       <c r="B675" s="3"/>
       <c r="C675" s="3"/>
@@ -6867,7 +6867,7 @@
       <c r="E675" s="4"/>
       <c r="F675" s="3"/>
     </row>
-    <row r="676" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A676" s="4"/>
       <c r="B676" s="3"/>
       <c r="C676" s="3"/>
@@ -6875,7 +6875,7 @@
       <c r="E676" s="4"/>
       <c r="F676" s="3"/>
     </row>
-    <row r="677" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A677" s="4"/>
       <c r="B677" s="3"/>
       <c r="C677" s="3"/>
@@ -6883,7 +6883,7 @@
       <c r="E677" s="4"/>
       <c r="F677" s="3"/>
     </row>
-    <row r="678" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A678" s="4"/>
       <c r="B678" s="3"/>
       <c r="C678" s="3"/>
@@ -6891,7 +6891,7 @@
       <c r="E678" s="4"/>
       <c r="F678" s="3"/>
     </row>
-    <row r="679" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A679" s="4"/>
       <c r="B679" s="3"/>
       <c r="C679" s="3"/>
@@ -6899,7 +6899,7 @@
       <c r="E679" s="4"/>
       <c r="F679" s="3"/>
     </row>
-    <row r="680" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A680" s="4"/>
       <c r="B680" s="3"/>
       <c r="C680" s="3"/>
@@ -6907,7 +6907,7 @@
       <c r="E680" s="4"/>
       <c r="F680" s="3"/>
     </row>
-    <row r="681" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A681" s="4"/>
       <c r="B681" s="3"/>
       <c r="C681" s="3"/>
@@ -6915,7 +6915,7 @@
       <c r="E681" s="4"/>
       <c r="F681" s="3"/>
     </row>
-    <row r="682" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A682" s="4"/>
       <c r="B682" s="3"/>
       <c r="C682" s="3"/>
@@ -6923,7 +6923,7 @@
       <c r="E682" s="4"/>
       <c r="F682" s="3"/>
     </row>
-    <row r="683" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A683" s="4"/>
       <c r="B683" s="3"/>
       <c r="C683" s="3"/>
@@ -6931,7 +6931,7 @@
       <c r="E683" s="4"/>
       <c r="F683" s="3"/>
     </row>
-    <row r="684" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A684" s="4"/>
       <c r="B684" s="3"/>
       <c r="C684" s="3"/>
@@ -6939,7 +6939,7 @@
       <c r="E684" s="4"/>
       <c r="F684" s="3"/>
     </row>
-    <row r="685" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A685" s="4"/>
       <c r="B685" s="3"/>
       <c r="C685" s="3"/>
@@ -6947,7 +6947,7 @@
       <c r="E685" s="4"/>
       <c r="F685" s="3"/>
     </row>
-    <row r="686" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A686" s="4"/>
       <c r="B686" s="3"/>
       <c r="C686" s="3"/>
@@ -6955,7 +6955,7 @@
       <c r="E686" s="4"/>
       <c r="F686" s="3"/>
     </row>
-    <row r="687" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A687" s="4"/>
       <c r="B687" s="3"/>
       <c r="C687" s="3"/>
@@ -6963,7 +6963,7 @@
       <c r="E687" s="4"/>
       <c r="F687" s="3"/>
     </row>
-    <row r="688" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A688" s="4"/>
       <c r="B688" s="3"/>
       <c r="C688" s="3"/>
@@ -6971,7 +6971,7 @@
       <c r="E688" s="4"/>
       <c r="F688" s="3"/>
     </row>
-    <row r="689" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A689" s="4"/>
       <c r="B689" s="3"/>
       <c r="C689" s="3"/>
@@ -6979,7 +6979,7 @@
       <c r="E689" s="4"/>
       <c r="F689" s="3"/>
     </row>
-    <row r="690" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A690" s="4"/>
       <c r="B690" s="3"/>
       <c r="C690" s="3"/>
@@ -6987,7 +6987,7 @@
       <c r="E690" s="4"/>
       <c r="F690" s="3"/>
     </row>
-    <row r="691" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A691" s="4"/>
       <c r="B691" s="3"/>
       <c r="C691" s="3"/>
@@ -6995,7 +6995,7 @@
       <c r="E691" s="4"/>
       <c r="F691" s="3"/>
     </row>
-    <row r="692" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A692" s="4"/>
       <c r="B692" s="3"/>
       <c r="C692" s="3"/>
@@ -7003,7 +7003,7 @@
       <c r="E692" s="4"/>
       <c r="F692" s="3"/>
     </row>
-    <row r="693" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A693" s="4"/>
       <c r="B693" s="3"/>
       <c r="C693" s="3"/>
@@ -7011,7 +7011,7 @@
       <c r="E693" s="4"/>
       <c r="F693" s="3"/>
     </row>
-    <row r="694" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A694" s="4"/>
       <c r="B694" s="3"/>
       <c r="C694" s="3"/>
@@ -7019,7 +7019,7 @@
       <c r="E694" s="4"/>
       <c r="F694" s="3"/>
     </row>
-    <row r="695" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A695" s="4"/>
       <c r="B695" s="3"/>
       <c r="C695" s="3"/>
@@ -7027,7 +7027,7 @@
       <c r="E695" s="4"/>
       <c r="F695" s="3"/>
     </row>
-    <row r="696" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A696" s="4"/>
       <c r="B696" s="3"/>
       <c r="C696" s="3"/>
@@ -7035,7 +7035,7 @@
       <c r="E696" s="4"/>
       <c r="F696" s="3"/>
     </row>
-    <row r="697" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A697" s="4"/>
       <c r="B697" s="3"/>
       <c r="C697" s="3"/>
@@ -7043,7 +7043,7 @@
       <c r="E697" s="4"/>
       <c r="F697" s="3"/>
     </row>
-    <row r="698" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A698" s="4"/>
       <c r="B698" s="3"/>
       <c r="C698" s="3"/>
@@ -7051,7 +7051,7 @@
       <c r="E698" s="4"/>
       <c r="F698" s="3"/>
     </row>
-    <row r="699" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A699" s="4"/>
       <c r="B699" s="3"/>
       <c r="C699" s="3"/>
@@ -7059,23 +7059,13 @@
       <c r="E699" s="4"/>
       <c r="F699" s="3"/>
     </row>
-    <row r="700" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A700" s="4"/>
       <c r="B700" s="3"/>
       <c r="C700" s="3"/>
       <c r="D700" s="4"/>
       <c r="E700" s="4"/>
       <c r="F700" s="3"/>
-    </row>
-    <row r="702" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D702" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="703" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D703" s="2" t="s">
-        <v>14</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -7109,277 +7099,277 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D1AE3BA-1A82-451D-B7CB-174ADC44D810}">
   <dimension ref="A1:A54"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
         <v>66</v>
       </c>
